--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -427,37 +427,37 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Melhor Envio</t>
+          <t>PicPay</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Developed and deployed a client segmentation model using K-prototypes clustering to support targeted marketing and data-driven decision making.</t>
+          <t>Redesigned client segmentation model, improving customer behavior insights and targeting.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Created and implemented an automated data pipeline to track client engagement stages, improving outreach efficiency and reducing churn risk; presented results to executive leadership.</t>
+          <t>Led A/B test design and analysis for home page, driving UX improvements.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Designed dashboards and refined company metrics, including churn definitions, to enhance analytical accuracy and support strategic business insights.</t>
+          <t>Developed PySpark data pipeline to streamline accountancy data processing.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -472,37 +472,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PicPay</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Led redesign of client segmentation model using Gaussian Mixture Modeling, enhancing feature engineering and validation to improve customer insights.</t>
+          <t>Developed and deployed a 21-day promotional sales forecasting model using LGBM.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Designed and analyzed A/B tests for home page experiments, driving data-driven decisions that informed product improvements.</t>
+          <t>Optimized pipeline runtime from 6 hours to 40 minutes via code vectorization and parallelization.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Developed data pipelines with PySpark and maintained performance dashboards to support analytical rigor and efficient reporting.</t>
+          <t>Implemented performance tracking and causal inference to validate model impact on sales.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -522,32 +522,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Ria Money Transfer</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Developed and deployed a 21-day sales forecasting model for promotional events, integrating it with the ERP system to support supply chain planning.</t>
+          <t>Developed daily country-level remittance volume forecasts, improving liquidity planning accuracy by ~10-12% MAPE.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Led the creation and optimization of a scalable ETL pipeline and parallelized model training, reducing processing time from 6 hours to 40 minutes using modular and vectorized code.</t>
+          <t>Built and deployed AWS-based data pipeline and ML models using LightGBM, ensuring reliable daily predictions.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Designed and implemented experimental and causal inference frameworks to evaluate model impact on sales and stock, collaborating with stakeholders to enhance data literacy and result interpretation.</t>
+          <t>Identified data leakage issues and enforced temporal consistency, enhancing model credibility and stakeholder trust.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -557,42 +557,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>recent_professional_experience</t>
+          <t>education</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>BSc, genetics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ria Money Transfer</t>
+          <t>UFRJ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Developed a production-ready forecasting system predicting daily remittance volumes at the country level, supporting liquidity planning and capital allocation across multiple markets.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Designed and implemented a robust data pipeline on AWS, ensuring temporal consistency and preventing data leakage through rigorous feature engineering and validation frameworks.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Collaborated with senior leadership to translate business needs into actionable models, improving transparency and reliability in forecasting to guide financial decision-making.</t>
+          <t>Involved from project conception to publication (as second author), in analyzing the phylogenetic relationships of dolphins using bayesian and maximum likelihood phylogenetic inference methods.</t>
         </is>
       </c>
       <c r="L5" t="b">
@@ -602,17 +592,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>recent_professional_experience</t>
+          <t>education</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CNCFlora</t>
+          <t>MSc, genetics</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>UFRJ</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -627,17 +617,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Integrated and standardized diverse biodiversity datasets using advanced R programming to support data-driven decision-making for species conservation prioritization.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Coordinated small project teams to address concurrent research tasks, ensuring alignment with the latest scientific knowledge and conservation policies.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Represented the institution in national and international forums, communicated technical research findings to stakeholders, and prepared progress reports on biodiversity goals for government agencies.</t>
+          <t>Interdisciplinary dissertation joining phylogenetic tree data and plant conservation data from CNCFlora to create a methodology to quantify the phylogenetic distinctness of brazilian endangered angiosperms</t>
         </is>
       </c>
       <c r="L6" t="b">
@@ -647,105 +627,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>education</t>
+          <t>academic_articles</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BSc, genetics</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>UFRJ</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2011</t>
+          <t>Skills &amp; stack</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Involved from project conception to publication (as second author), in analyzing the phylogenetic relationships of dolphins using bayesian and maximum likelihood phylogenetic inference methods.</t>
+          <t>My area of expertise is tilted towards using statistics (Machine Learning included) to describe and understand client behavior, development of predictive models (e.g. churn or propension) and client segmentation using unsupervised ML. I have experience developing *ad hoc* analyses and also developing production ready models.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Statistical modeling, data analysis and hypothesis testing are considered staple knowledge in the area I graduated from. This fact allowed me to transit between different technical areas seamlessly (such as machine learning, A/B testing and data visualization).</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>R is my language of choice, but I also have proficiency with Python, SQL and Spark (PySpark/Sparklyr). I work comfortably with git, github and Linux, besides also having experience working with the Data Bricks environment (and with notebooks in general) and AWS (e.g. Redshift and S3).</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>I have worked in several research projects with people from a wide array of backgrounds and seniority levels, some of which from end-to-end. I have been well trained since an undergrad to explain technical subjects to non technical audiences.</t>
         </is>
       </c>
       <c r="L7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>education</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>MSc, genetics</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>UFRJ</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Interdisciplinary dissertation joining phylogenetic tree data and plant conservation data from CNCFlora to create a methodology to quantify the phylogenetic distinctness of brazilian endangered angiosperms</t>
-        </is>
-      </c>
-      <c r="L8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>academic_articles</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Skills &amp; stack</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>My area of expertise is tilted towards using statistics (Machine Learning included) to describe and understand client behavior, development of predictive models (e.g. churn or propension) and client segmentation using unsupervised ML. I have experience developing *ad hoc* analyses and also developing production ready models.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Statistical modeling, data analysis and hypothesis testing are considered staple knowledge in the area I graduated from. This fact allowed me to transit between different technical areas seamlessly (such as machine learning, A/B testing and data visualization).</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>R is my language of choice, but I also have proficiency with Python, SQL and Spark (PySpark/Sparklyr). I work comfortably with git, github and Linux, besides also having experience working with the Data Bricks environment (and with notebooks in general) and AWS (e.g. Redshift and S3).</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>I have worked in several research projects with people from a wide array of backgrounds and seniority levels, some of which from end-to-end. I have been well trained since an undergrad to explain technical subjects to non technical audiences.</t>
-        </is>
-      </c>
-      <c r="L9" t="b">
         <v>1</v>
       </c>
     </row>

--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -447,17 +447,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Redesigned client segmentation model, improving customer behavior insights and targeting.</t>
+          <t>Led the redevelopment of the client segmentation model using Gaussian Mixture Modeling, applying feature engineering, hypothesis testing, and descriptive statistics to enhance clustering accuracy and business relevance.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Led A/B test design and analysis for home page, driving UX improvements.</t>
+          <t>Designed and analyzed A/B tests to optimize home page performance, maintaining key performance metric dashboards and supporting data-driven decision-making across teams.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Developed PySpark data pipeline to streamline accountancy data processing.</t>
+          <t>Developed scalable data pipelines with PySpark for processing and organizing large accountancy datasets, improving data accessibility and supporting supervised machine learning initiatives for targeted analyses.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -492,17 +492,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Developed and deployed a 21-day promotional sales forecasting model using LGBM.</t>
+          <t>Led the development and deployment of a scalable, parallelized ML forecasting pipeline using Vertex AI and Kubeflow, reducing runtime from 6 hours to 40 minutes and enabling daily sales predictions for promotional events.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Optimized pipeline runtime from 6 hours to 40 minutes via code vectorization and parallelization.</t>
+          <t>Designed and implemented a rigorous experimental framework with hypothesis testing and causal inference to assess model impact on sales accuracy and inventory optimization, supporting risk analysis and continuous performance monitoring.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Implemented performance tracking and causal inference to validate model impact on sales.</t>
+          <t>Collaborated with stakeholders and data leadership to enhance transparency, explain statistical results, and guide strategic decisions using robust metrics like MAPE and wMAPE, improving adoption and model governance.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -537,17 +537,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Developed daily country-level remittance volume forecasts, improving liquidity planning accuracy by ~10-12% MAPE.</t>
+          <t>Led the development of a production-grade forecasting system using LightGBM and ensemble methods to predict daily remittance volumes, improving liquidity planning and capital allocation across multiple markets.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Built and deployed AWS-based data pipeline and ML models using LightGBM, ensuring reliable daily predictions.</t>
+          <t>Designed and implemented robust, time-aware data pipelines and validation frameworks in AWS (S3, Athena), eliminating data leakage and ensuring temporal consistency for reliable model performance (~10–12% MAPE).</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Identified data leakage issues and enforced temporal consistency, enhancing model credibility and stakeholder trust.</t>
+          <t>Collaborated with senior stakeholders to translate business requirements into quantitative solutions, enhancing transparency, regulatory compliance, and decision-making around liquidity and operational risk.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -637,22 +637,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>My area of expertise is tilted towards using statistics (Machine Learning included) to describe and understand client behavior, development of predictive models (e.g. churn or propension) and client segmentation using unsupervised ML. I have experience developing *ad hoc* analyses and also developing production ready models.</t>
+          <t>Developed predictive ML models for client behavior and segmentation</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Statistical modeling, data analysis and hypothesis testing are considered staple knowledge in the area I graduated from. This fact allowed me to transit between different technical areas seamlessly (such as machine learning, A/B testing and data visualization).</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>R is my language of choice, but I also have proficiency with Python, SQL and Spark (PySpark/Sparklyr). I work comfortably with git, github and Linux, besides also having experience working with the Data Bricks environment (and with notebooks in general) and AWS (e.g. Redshift and S3).</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>I have worked in several research projects with people from a wide array of backgrounds and seniority levels, some of which from end-to-end. I have been well trained since an undergrad to explain technical subjects to non technical audiences.</t>
+          <t>Proficient in Python, SQL, R, Spark, and cloud environments (AWS, Databricks)</t>
         </is>
       </c>
       <c r="L7" t="b">

--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -447,17 +447,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Led the redevelopment of the client segmentation model using Gaussian Mixture Modeling, applying feature engineering, hypothesis testing, and descriptive statistics to enhance clustering accuracy and business relevance.</t>
+          <t>Led redesign of client segmentation using Gaussian Mixture Modeling, enhancing feature engineering and model assumptions validation.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Designed and analyzed A/B tests to optimize home page performance, maintaining key performance metric dashboards and supporting data-driven decision-making across teams.</t>
+          <t>Managed A/B test design and analysis for home page experiments, driving data-informed product improvements.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Developed scalable data pipelines with PySpark for processing and organizing large accountancy datasets, improving data accessibility and supporting supervised machine learning initiatives for targeted analyses.</t>
+          <t>Developed and maintained performance dashboards and data pipelines with Databricks, Python, SQL, and PySpark for operational insights.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -492,17 +492,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Led the development and deployment of a scalable, parallelized ML forecasting pipeline using Vertex AI and Kubeflow, reducing runtime from 6 hours to 40 minutes and enabling daily sales predictions for promotional events.</t>
+          <t>Developed and deployed a 21-day sales forecasting model for promotional events, improving demand predictability and supply planning.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Designed and implemented a rigorous experimental framework with hypothesis testing and causal inference to assess model impact on sales accuracy and inventory optimization, supporting risk analysis and continuous performance monitoring.</t>
+          <t>Led creation of parallelized ETL and modeling pipelines, reducing runtime from 6 hours to 40 minutes through code optimization.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Collaborated with stakeholders and data leadership to enhance transparency, explain statistical results, and guide strategic decisions using robust metrics like MAPE and wMAPE, improving adoption and model governance.</t>
+          <t>Designed and implemented experimental methodology and performance database to measure model impact and monitor KPIs with stakeholders.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -537,17 +537,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Led the development of a production-grade forecasting system using LightGBM and ensemble methods to predict daily remittance volumes, improving liquidity planning and capital allocation across multiple markets.</t>
+          <t>Developed a production-grade forecasting system predicting daily remittance volumes, enhancing liquidity planning and capital allocation across markets.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Designed and implemented robust, time-aware data pipelines and validation frameworks in AWS (S3, Athena), eliminating data leakage and ensuring temporal consistency for reliable model performance (~10–12% MAPE).</t>
+          <t>Designed robust data pipelines using AWS (S3, Athena) and implemented tree-based ML models with rigorous time-aware validation frameworks.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Collaborated with senior stakeholders to translate business requirements into quantitative solutions, enhancing transparency, regulatory compliance, and decision-making around liquidity and operational risk.</t>
+          <t>Identified and resolved data leakage issues in feature engineering, improving forecast reliability and establishing reproducible production pipelines with Docker and ECS.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -637,12 +637,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Developed predictive ML models for client behavior and segmentation</t>
+          <t>Applied statistical modeling and machine learning techniques to analyze client behavior, develop predictive models for churn and propensity, and perform client segmentation using unsupervised learning.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Proficient in Python, SQL, R, Spark, and cloud environments (AWS, Databricks)</t>
+          <t>Skilled in developing production-ready models and conducting ad hoc analyses, leveraging expertise in hypothesis testing, A/B testing, and data visualization.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Proficient in R, Python, SQL, and Spark, with experience in version control (git), Linux environments, cloud platforms (AWS Redshift, S3), and collaborative tools such as Data Bricks notebooks.</t>
         </is>
       </c>
       <c r="L7" t="b">

--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -447,17 +447,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Led redesign of client segmentation using Gaussian Mixture Modeling, enhancing feature engineering and model assumptions validation.</t>
+          <t>Led A/B test designs and analysis for homepage experiments, improving client behavior insights and driving feature optimization.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Managed A/B test design and analysis for home page experiments, driving data-informed product improvements.</t>
+          <t>Redesigned client segmentation model using Gaussian Mixture Modeling and feature engineering to enhance transaction behavior understanding.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Developed and maintained performance dashboards and data pipelines with Databricks, Python, SQL, and PySpark for operational insights.</t>
+          <t>Developed and maintained data pipelines with PySpark and Databricks to streamline performance dashboards and support financial reporting.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -492,17 +492,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Developed and deployed a 21-day sales forecasting model for promotional events, improving demand predictability and supply planning.</t>
+          <t>Developed and deployed an end-to-end sales forecasting model predicting promotional event demand 21 days in advance, integrated with ERP.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Led creation of parallelized ETL and modeling pipelines, reducing runtime from 6 hours to 40 minutes through code optimization.</t>
+          <t>Optimized data pipelines and parallelized daily training for store-specific models, reducing runtime from 6 hours to 40 minutes.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Designed and implemented experimental methodology and performance database to measure model impact and monitor KPIs with stakeholders.</t>
+          <t>Designed experimental framework and performance database to measure model impact, improving stock management and sales predictability.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -537,17 +537,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Developed a production-grade forecasting system predicting daily remittance volumes, enhancing liquidity planning and capital allocation across markets.</t>
+          <t>Developed a production-grade forecasting system using LightGBM to predict daily remittance volumes, improving capital allocation across countries.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Designed robust data pipelines using AWS (S3, Athena) and implemented tree-based ML models with rigorous time-aware validation frameworks.</t>
+          <t>Designed and implemented a robust AWS data pipeline with S3 and Athena, ensuring consistent datasets and preventing data leakage through strict temporal feature engineering.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Identified and resolved data leakage issues in feature engineering, improving forecast reliability and establishing reproducible production pipelines with Docker and ECS.</t>
+          <t>Led production deployment via Docker and ECS, enhancing pipeline scalability and reproducibility, while collaborating with finance leadership to align models with business goals.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -637,17 +637,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Applied statistical modeling and machine learning techniques to analyze client behavior, develop predictive models for churn and propensity, and perform client segmentation using unsupervised learning.</t>
+          <t>Specialize in applying statistical methods and machine learning to analyze client behavior, develop predictive models, and perform client segmentation using unsupervised techniques.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Skilled in developing production-ready models and conducting ad hoc analyses, leveraging expertise in hypothesis testing, A/B testing, and data visualization.</t>
+          <t>Proficient in statistical modeling, hypothesis testing, A/B testing, and data visualization with strong adaptability across technical disciplines.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Proficient in R, Python, SQL, and Spark, with experience in version control (git), Linux environments, cloud platforms (AWS Redshift, S3), and collaborative tools such as Data Bricks notebooks.</t>
+          <t>Experienced with R, Python, SQL, Spark (PySpark/Sparklyr), git, Linux, Data Bricks, and AWS services including Redshift and S3 for scalable data analysis and production model deployment.</t>
         </is>
       </c>
       <c r="L7" t="b">

--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -447,17 +447,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Led A/B test designs and analysis for homepage experiments, improving client behavior insights and driving feature optimization.</t>
+          <t>Redesigned outdated client segmentation using Gaussian Mixture Modeling, improving feature engineering and cluster validity for credit analysis.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Redesigned client segmentation model using Gaussian Mixture Modeling and feature engineering to enhance transaction behavior understanding.</t>
+          <t>Developed PySpark data pipeline to streamline accountancy data processing, enhancing data lake integration and analytical efficiency.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Developed and maintained data pipelines with PySpark and Databricks to streamline performance dashboards and support financial reporting.</t>
+          <t>Led A/B test designs and analyses on home page experimentation for data-driven customer behavior insights and model validation.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -492,17 +492,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Developed and deployed an end-to-end sales forecasting model predicting promotional event demand 21 days in advance, integrated with ERP.</t>
+          <t>Developed and deployed a scalable lgbm forecasting model predicting promotional sales 21 days ahead, saving $4M monthly in overstock costs.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Optimized data pipelines and parallelized daily training for store-specific models, reducing runtime from 6 hours to 40 minutes.</t>
+          <t>Led creation of an optimized ETL pipeline and parallelized daily retraining using Vertex AI and Kubeflow, reducing runtime from 6 hours to 40 minutes.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Designed experimental framework and performance database to measure model impact, improving stock management and sales predictability.</t>
+          <t>Designed and implemented causal inference testing framework and performance database for robust model monitoring and decision impact assessment.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -537,17 +537,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Developed a production-grade forecasting system using LightGBM to predict daily remittance volumes, improving capital allocation across countries.</t>
+          <t>Developed a production-grade forecasting system using LightGBM and ensemble models, achieving 10–12% MAPE to improve liquidity planning and capital allocation.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Designed and implemented a robust AWS data pipeline with S3 and Athena, ensuring consistent datasets and preventing data leakage through strict temporal feature engineering.</t>
+          <t>Designed and implemented a robust AWS-based data pipeline (S3, Athena) with strict temporal validation, eliminating data leakage and enhancing model reliability.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Led production deployment via Docker and ECS, enhancing pipeline scalability and reproducibility, while collaborating with finance leadership to align models with business goals.</t>
+          <t>Led production deployment with containerized AWS infrastructure (Docker, ECS, ECR), modularizing codebase to ensure scalability and maintainability of daily forecasts.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -637,17 +637,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Specialize in applying statistical methods and machine learning to analyze client behavior, develop predictive models, and perform client segmentation using unsupervised techniques.</t>
+          <t>Expertise in statistical modeling and machine learning for client behavior analysis, predictive model development, and unsupervised segmentation to enhance credit decision-making processes.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Proficient in statistical modeling, hypothesis testing, A/B testing, and data visualization with strong adaptability across technical disciplines.</t>
+          <t>Proficient in Python, SQL, R, and Spark (PySpark, Sparklyr), with practical experience in scalable ML model deployment using DataBricks, AWS (Redshift, S3), and version control via Git/GitHub in Linux environments.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Experienced with R, Python, SQL, Spark (PySpark/Sparklyr), git, Linux, Data Bricks, and AWS services including Redshift and S3 for scalable data analysis and production model deployment.</t>
+          <t>Skilled in full model lifecycle management, including hypothesis testing, A/B experimentation, data visualization, and translating complex analytical results for diverse technical and non-technical stakeholders.</t>
         </is>
       </c>
       <c r="L7" t="b">

--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -447,17 +447,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Redesigned outdated client segmentation using Gaussian Mixture Modeling, improving feature engineering and cluster validity for credit analysis.</t>
+          <t>Analyzed A/B test results and proposed experimental designs to optimize home page user engagement using statistical methods.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Developed PySpark data pipeline to streamline accountancy data processing, enhancing data lake integration and analytical efficiency.</t>
+          <t>Redesigned client segmentation model with Gaussian Mixture Modeling, incorporating feature engineering and hypothesis testing for improved customer clustering.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Led A/B test designs and analyses on home page experimentation for data-driven customer behavior insights and model validation.</t>
+          <t>Developed data pipelines and performed data wrangling with PySpark, R, and SQL to support financial reporting and cost reduction in customer service.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -492,17 +492,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Developed and deployed a scalable lgbm forecasting model predicting promotional sales 21 days ahead, saving $4M monthly in overstock costs.</t>
+          <t>Developed causal inference methodology to evaluate diagnostic model impact, enhancing accuracy and reliability in clinical test assessments.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Led creation of an optimized ETL pipeline and parallelized daily retraining using Vertex AI and Kubeflow, reducing runtime from 6 hours to 40 minutes.</t>
+          <t>Supported regulatory submissions by performing interim analyses and sample size calculations, ensuring compliance with clinical study protocols.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Designed and implemented causal inference testing framework and performance database for robust model monitoring and decision impact assessment.</t>
+          <t>Collaborated with interdisciplinary international teams, delivering statistical expertise and clear communication to optimize diagnostic test development.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -537,17 +537,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Developed a production-grade forecasting system using LightGBM and ensemble models, achieving 10–12% MAPE to improve liquidity planning and capital allocation.</t>
+          <t>Supported diagnostic test submissions by collaborating with Regulatory Affairs and Clinical Operations to meet regulatory requirements for clinical studies.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Designed and implemented a robust AWS-based data pipeline (S3, Athena) with strict temporal validation, eliminating data leakage and enhancing model reliability.</t>
+          <t>Developed and validated R packages to enhance test development tools, improving analysis efficiency and documentation compliance.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Led production deployment with containerized AWS infrastructure (Docker, ECS, ECR), modularizing codebase to ensure scalability and maintainability of daily forecasts.</t>
+          <t>Conducted interim analyses and sample size calculations, communicating statistical insights clearly to interdisciplinary teams and study managers.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -637,17 +637,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Expertise in statistical modeling and machine learning for client behavior analysis, predictive model development, and unsupervised segmentation to enhance credit decision-making processes.</t>
+          <t>Applied statistical modeling, hypothesis testing, and machine learning techniques to develop predictive models and client segmentation, enhancing analytical insights.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Proficient in Python, SQL, R, and Spark (PySpark, Sparklyr), with practical experience in scalable ML model deployment using DataBricks, AWS (Redshift, S3), and version control via Git/GitHub in Linux environments.</t>
+          <t>Proficient in R programming for data analysis and statistical modeling, with additional experience in Python, SQL, and Spark to support diverse data environments.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Skilled in full model lifecycle management, including hypothesis testing, A/B experimentation, data visualization, and translating complex analytical results for diverse technical and non-technical stakeholders.</t>
+          <t>Collaborated in multidisciplinary research projects, effectively communicating complex statistical concepts to both technical and non-technical audiences.</t>
         </is>
       </c>
       <c r="L7" t="b">

--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -447,17 +447,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Analyzed A/B test results and proposed experimental designs to optimize home page user engagement using statistical methods.</t>
+          <t>Analyzed A/B test performance and designed experiments to improve homepage client engagement and metrics.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Redesigned client segmentation model with Gaussian Mixture Modeling, incorporating feature engineering and hypothesis testing for improved customer clustering.</t>
+          <t>Developed and maintained KR dashboards consolidating key performance indicators for the experimentation squad.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Developed data pipelines and performed data wrangling with PySpark, R, and SQL to support financial reporting and cost reduction in customer service.</t>
+          <t>Applied unsupervised learning and feature engineering to customer segmentation, enhancing behavioral insight and model accuracy.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -492,17 +492,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Developed causal inference methodology to evaluate diagnostic model impact, enhancing accuracy and reliability in clinical test assessments.</t>
+          <t>Developed causal inference methodology to evaluate and quantify model impacts on medical test performance.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Supported regulatory submissions by performing interim analyses and sample size calculations, ensuring compliance with clinical study protocols.</t>
+          <t>Programmed and validated R package functions to support statistical analysis and regulatory documentation requirements.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Collaborated with interdisciplinary international teams, delivering statistical expertise and clear communication to optimize diagnostic test development.</t>
+          <t>Presented interim clinical study analysis findings to cross-functional teams, influencing project decisions and action plans.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -537,17 +537,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Supported diagnostic test submissions by collaborating with Regulatory Affairs and Clinical Operations to meet regulatory requirements for clinical studies.</t>
+          <t>Supported medical test submissions by developing and validating statistical analysis tools in R and SAS.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Developed and validated R packages to enhance test development tools, improving analysis efficiency and documentation compliance.</t>
+          <t>Collaborated with cross-functional teams to address assay variance issues and improve test precision through detailed analysis.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Conducted interim analyses and sample size calculations, communicating statistical insights clearly to interdisciplinary teams and study managers.</t>
+          <t>Conducted interim analyses and sample size calculations, ensuring regulatory compliance and effective project planning.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -637,17 +637,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Applied statistical modeling, hypothesis testing, and machine learning techniques to develop predictive models and client segmentation, enhancing analytical insights.</t>
+          <t>Developed predictive models and performed client segmentation using statistical modelling and machine learning techniques, primarily utilizing R programming.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Proficient in R programming for data analysis and statistical modeling, with additional experience in Python, SQL, and Spark to support diverse data environments.</t>
+          <t>Conducted statistical analyses, hypothesis testing, and data visualization with proficiency in R, Python, SQL, and Spark environments, supporting end-to-end research projects.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Collaborated in multidisciplinary research projects, effectively communicating complex statistical concepts to both technical and non-technical audiences.</t>
+          <t>Collaborated effectively in multidisciplinary teams, communicating complex statistical concepts clearly to both technical and non-technical audiences.</t>
         </is>
       </c>
       <c r="L7" t="b">

--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -447,17 +447,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Analyzed A/B test performance and designed experiments to improve homepage client engagement and metrics.</t>
+          <t>Analyzed A/B test results and designed experiments to optimize the PicPay home page, enhancing user engagement through rigorous analytics.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Developed and maintained KR dashboards consolidating key performance indicators for the experimentation squad.</t>
+          <t>Redesigned the outdated Gaussian Mixture Model–based client segmentation, applying feature engineering and statistical validation techniques.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Applied unsupervised learning and feature engineering to customer segmentation, enhancing behavioral insight and model accuracy.</t>
+          <t>Developed and maintained key performance dashboards to monitor team metrics, ensuring data-driven decision-making and operational transparency.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -492,17 +492,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Developed causal inference methodology to evaluate and quantify model impacts on medical test performance.</t>
+          <t>Developed an end-to-end forecasting model predicting promotional sales 21 days ahead, improving demand planning for supply teams.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Programmed and validated R package functions to support statistical analysis and regulatory documentation requirements.</t>
+          <t>Led creation of an orchestrated ETL pipeline ensuring clean, timely sales data availability for analytics and supply chain alignment.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Presented interim clinical study analysis findings to cross-functional teams, influencing project decisions and action plans.</t>
+          <t>Collaborated with MLOps team to deploy parallelized daily sales prediction pipelines using Vertex AI and Kubeflow, enabling scalable forecasting.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -537,17 +537,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Supported medical test submissions by developing and validating statistical analysis tools in R and SAS.</t>
+          <t>Developed a country-level forecasting system predicting daily remittance volumes (T+1) to optimize liquidity planning and capital allocation across markets.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Collaborated with cross-functional teams to address assay variance issues and improve test precision through detailed analysis.</t>
+          <t>Designed robust data pipelines integrating AWS S3 and Athena to ensure consistent, reliable data for model training and validation.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Conducted interim analyses and sample size calculations, ensuring regulatory compliance and effective project planning.</t>
+          <t>Built machine learning models using LightGBM and ensemble methods with advanced experiment design for realistic, stable volume forecasts.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -637,17 +637,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Developed predictive models and performed client segmentation using statistical modelling and machine learning techniques, primarily utilizing R programming.</t>
+          <t>Specialized in statistical modeling and machine learning to analyze client behavior, develop predictive models, and execute client segmentation.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Conducted statistical analyses, hypothesis testing, and data visualization with proficiency in R, Python, SQL, and Spark environments, supporting end-to-end research projects.</t>
+          <t>Experienced in creating ad hoc analyses and deploying production-ready predictive models for business applications.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Collaborated effectively in multidisciplinary teams, communicating complex statistical concepts clearly to both technical and non-technical audiences.</t>
+          <t>Proficient in data science techniques including hypothesis testing, A/B testing, and data visualization for actionable insights.</t>
         </is>
       </c>
       <c r="L7" t="b">

--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -447,17 +447,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Analyzed A/B test results and designed experiments to optimize the PicPay home page, enhancing user engagement through rigorous analytics.</t>
+          <t>Led redesign of client segmentation model using Gaussian Mixture Modeling, improving feature engineering and validating model assumptions with statistical methods.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Redesigned the outdated Gaussian Mixture Model–based client segmentation, applying feature engineering and statistical validation techniques.</t>
+          <t>Analyzed A/B test performance on homepage experiments, proposing test designs to optimize user engagement and behavior understanding.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Developed and maintained key performance dashboards to monitor team metrics, ensuring data-driven decision-making and operational transparency.</t>
+          <t>Maintained key performance metric dashboards for the experimentation squad, ensuring accurate tracking of team objectives and outcomes.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -492,17 +492,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Developed an end-to-end forecasting model predicting promotional sales 21 days ahead, improving demand planning for supply teams.</t>
+          <t>Developed and deployed a parallelized sales forecasting model using lgbm, Vertex AI, and Kubeflow pipelines, improving predictive accuracy for promotional events.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Led creation of an orchestrated ETL pipeline ensuring clean, timely sales data availability for analytics and supply chain alignment.</t>
+          <t>Led creation of an orchestrated ETL pipeline to provide clean, accessible sales data to supply teams, enabling efficient forecasting workflows.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Collaborated with MLOps team to deploy parallelized daily sales prediction pipelines using Vertex AI and Kubeflow, enabling scalable forecasting.</t>
+          <t>Optimized forecasting code by rewriting pandas scripts into polars, reducing runtime from 6 hours to 40 minutes for daily training of store-specific models.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -537,17 +537,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Developed a country-level forecasting system predicting daily remittance volumes (T+1) to optimize liquidity planning and capital allocation across markets.</t>
+          <t>Developed a production-grade forecasting system predicting daily country-level remittance volumes, improving liquidity planning and capital allocation accuracy.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Designed robust data pipelines integrating AWS S3 and Athena to ensure consistent, reliable data for model training and validation.</t>
+          <t>Designed a robust AWS-based data pipeline integrating S3 and Athena sources, ensuring reliable data for modeling and validation workflows.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Built machine learning models using LightGBM and ensemble methods with advanced experiment design for realistic, stable volume forecasts.</t>
+          <t>Built machine learning models using LightGBM and ensemble methods with time-aware validation to produce stable forecasts achieving ~10-12% MAPE.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -637,17 +637,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Specialized in statistical modeling and machine learning to analyze client behavior, develop predictive models, and execute client segmentation.</t>
+          <t>Specialize in using statistical methods and machine learning to analyze client behavior, develop predictive models, and perform client segmentation with unsupervised learning.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Experienced in creating ad hoc analyses and deploying production-ready predictive models for business applications.</t>
+          <t>Skilled in creating ad hoc analyses and building production-level models to support business decision-making processes.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Proficient in data science techniques including hypothesis testing, A/B testing, and data visualization for actionable insights.</t>
+          <t>Strong foundation in statistical modeling, data analysis, and hypothesis testing, enabling seamless transitions between machine learning, A/B testing, and data visualization.</t>
         </is>
       </c>
       <c r="L7" t="b">

--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -447,17 +447,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Led redesign of client segmentation model using Gaussian Mixture Modeling, improving feature engineering and validating model assumptions with statistical methods.</t>
+          <t>Redesigned FMCG client segmentation model using Gaussian Mixture Modeling, feature engineering, and statistical validation to enhance behavioral insights.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Analyzed A/B test performance on homepage experiments, proposing test designs to optimize user engagement and behavior understanding.</t>
+          <t>Led A/B test experimental design and analysis for homepage redesign, improving user engagement through robust statistical modeling.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Maintained key performance metric dashboards for the experimentation squad, ensuring accurate tracking of team objectives and outcomes.</t>
+          <t>Developed and maintained key performance metric dashboard using Python, SQL, and Databricks to monitor team results and guide strategies.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -492,17 +492,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Developed and deployed a parallelized sales forecasting model using lgbm, Vertex AI, and Kubeflow pipelines, improving predictive accuracy for promotional events.</t>
+          <t>Developed and deployed FMCG sales forecasting model for promotional events, improving predictability with MAPE-driven validation and savings over $4M monthly.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Led creation of an orchestrated ETL pipeline to provide clean, accessible sales data to supply teams, enabling efficient forecasting workflows.</t>
+          <t>Led ETL pipeline orchestration for clean product sales data, enabling reliable daily forecasting and integration with Carrefour’s ERP system.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Optimized forecasting code by rewriting pandas scripts into polars, reducing runtime from 6 hours to 40 minutes for daily training of store-specific models.</t>
+          <t>Collaborated with ML Ops to deploy parallelized sales prediction pipelines on Vertex AI, reducing processing time from 6 hours to 40 minutes using Python optimization.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -537,17 +537,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Developed a production-grade forecasting system predicting daily country-level remittance volumes, improving liquidity planning and capital allocation accuracy.</t>
+          <t>Developed and deployed machine learning forecasting models using LightGBM for daily remittance volumes, achieving ~10-12% MAPE and improving liquidity allocation.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Designed a robust AWS-based data pipeline integrating S3 and Athena sources, ensuring reliable data for modeling and validation workflows.</t>
+          <t>Designed robust data pipelines on AWS (S3, Athena) ensuring temporal consistency and preventing data leakage during feature engineering for reliable FMCG predictive analytics.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Built machine learning models using LightGBM and ensemble methods with time-aware validation to produce stable forecasts achieving ~10-12% MAPE.</t>
+          <t>Implemented time-aware validation frameworks simulating production environments, enhancing the credibility and stability of forecasting models under real operational conditions.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -637,17 +637,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Specialize in using statistical methods and machine learning to analyze client behavior, develop predictive models, and perform client segmentation with unsupervised learning.</t>
+          <t>Applied statistical modeling, machine learning, and predictive analytics to understand client behavior and develop churn and propensity models.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Skilled in creating ad hoc analyses and building production-level models to support business decision-making processes.</t>
+          <t>Performed client segmentation using unsupervised machine learning techniques to identify meaningful customer groups.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Strong foundation in statistical modeling, data analysis, and hypothesis testing, enabling seamless transitions between machine learning, A/B testing, and data visualization.</t>
+          <t>Developed ad hoc analyses and production-ready models, integrating hypothesis testing and data visualization to support insights.</t>
         </is>
       </c>
       <c r="L7" t="b">

--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -447,17 +447,22 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Redesigned FMCG client segmentation model using Gaussian Mixture Modeling, feature engineering, and statistical validation to enhance behavioral insights.</t>
+          <t>Recreated and validated client segmentation model using Gaussian Mixture Modeling, enhancing feature engineering and statistical testing for improved clustering accuracy.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Led A/B test experimental design and analysis for homepage redesign, improving user engagement through robust statistical modeling.</t>
+          <t>Designed and analyzed A/B tests for the homepage, influencing user engagement through rigorous experimentation and performance metric monitoring.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Developed and maintained key performance metric dashboard using Python, SQL, and Databricks to monitor team results and guide strategies.</t>
+          <t>Developed a PySpark data pipeline to structure and analyze complex accounting data, supporting financial reporting and operational insights.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Maintained and updated the squad’s Key Results dashboard, tracking performance metrics and ensuring data-driven decision-making transparency.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -492,17 +497,22 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Developed and deployed FMCG sales forecasting model for promotional events, improving predictability with MAPE-driven validation and savings over $4M monthly.</t>
+          <t>Developed and deployed a 21-day promotional sales forecasting model for FMCG, achieving 20% MAPE and improving supply planning accuracy.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Led ETL pipeline orchestration for clean product sales data, enabling reliable daily forecasting and integration with Carrefour’s ERP system.</t>
+          <t>Led creation of an orchestrated ETL pipeline to clean and centralize sales data, enabling daily parallel sales model training per store.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Collaborated with ML Ops to deploy parallelized sales prediction pipelines on Vertex AI, reducing processing time from 6 hours to 40 minutes using Python optimization.</t>
+          <t>Collaborated with MLOps team to deploy scalable forecasting pipelines using Vertex AI and Kubeflow, reducing runtime from 6 hours to 40 minutes.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Designed and implemented causal inference methodologies to evaluate model impact, guiding decisions based on sales and stock hypothesis testing.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -537,17 +547,22 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Developed and deployed machine learning forecasting models using LightGBM for daily remittance volumes, achieving ~10-12% MAPE and improving liquidity allocation.</t>
+          <t>Developed and deployed a production-grade LightGBM forecasting system with 10-15% MAPE, improving liquidity planning in international remittance markets.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Designed robust data pipelines on AWS (S3, Athena) ensuring temporal consistency and preventing data leakage during feature engineering for reliable FMCG predictive analytics.</t>
+          <t>Engineered data pipelines in AWS (S3, Athena), ensuring reliable data integration and temporal consistency for robust machine learning model training and validation.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Implemented time-aware validation frameworks simulating production environments, enhancing the credibility and stability of forecasting models under real operational conditions.</t>
+          <t>Identified and eliminated multiple data leakage issues, restructuring feature engineering to enforce strict temporal cutoffs and achieve realistic model accuracy.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Built time-aware validation frameworks simulating production environments, enhancing model credibility and supporting accurate daily country-level remittance volume forecasts.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -637,17 +652,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Applied statistical modeling, machine learning, and predictive analytics to understand client behavior and develop churn and propensity models.</t>
+          <t>Specialize in applying statistical and machine learning techniques to model client behavior, churn prediction, and segmentation using unsupervised ML methods.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Performed client segmentation using unsupervised machine learning techniques to identify meaningful customer groups.</t>
+          <t>Develop both ad hoc analyses and production-ready predictive models to support business decision-making and forecasting.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Developed ad hoc analyses and production-ready models, integrating hypothesis testing and data visualization to support insights.</t>
+          <t>Proficient in statistical modeling, hypothesis testing, and machine learning, enabling seamless transition across data science domains including experimentation and visualization.</t>
         </is>
       </c>
       <c r="L7" t="b">

--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -447,22 +447,22 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Recreated and validated client segmentation model using Gaussian Mixture Modeling, enhancing feature engineering and statistical testing for improved clustering accuracy.</t>
+          <t>Redesigned client segmentation model using Gaussian Mixture Modeling, applying feature engineering and hypothesis testing to validate new variables.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Designed and analyzed A/B tests for the homepage, influencing user engagement through rigorous experimentation and performance metric monitoring.</t>
+          <t>Designed and analyzed A/B tests for home page redesign, improving experimental robustness and guiding stakeholder decisions with clear insights.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Developed a PySpark data pipeline to structure and analyze complex accounting data, supporting financial reporting and operational insights.</t>
+          <t>Developed PySpark data pipelines to process and structure complex accountancy data, enhancing data accessibility and accuracy for financial reporting.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Maintained and updated the squad’s Key Results dashboard, tracking performance metrics and ensuring data-driven decision-making transparency.</t>
+          <t>Mentored junior analysts in statistical methods, experimentation, and machine learning deployment, fostering team analytical capabilities and best practices.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -497,22 +497,22 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Developed and deployed a 21-day promotional sales forecasting model for FMCG, achieving 20% MAPE and improving supply planning accuracy.</t>
+          <t>Developed and deployed ML forecasting model predicting promotional sales 21 days ahead, achieving 20% MAPE for FMCG product demand.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Led creation of an orchestrated ETL pipeline to clean and centralize sales data, enabling daily parallel sales model training per store.</t>
+          <t>Led creation of ETL pipeline integrating product sales data for supply teams, enabling informed inventory decision-making and forecasting accuracy.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Collaborated with MLOps team to deploy scalable forecasting pipelines using Vertex AI and Kubeflow, reducing runtime from 6 hours to 40 minutes.</t>
+          <t>Collaborated with MLOps to deploy daily parallelized sales prediction pipeline using Vertex AI and Kubeflow, reducing process time from 6 hours to 40 minutes.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Designed and implemented causal inference methodologies to evaluate model impact, guiding decisions based on sales and stock hypothesis testing.</t>
+          <t>Implemented experimental design with causal inference, measuring model impact through hypothesis testing against baseline sales and stock surplus averages.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -547,22 +547,22 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Developed and deployed a production-grade LightGBM forecasting system with 10-15% MAPE, improving liquidity planning in international remittance markets.</t>
+          <t>Developed and deployed forecasting models predicting daily remittance volumes at a country level with 10–15% MAPE across markets.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Engineered data pipelines in AWS (S3, Athena), ensuring reliable data integration and temporal consistency for robust machine learning model training and validation.</t>
+          <t>Designed robust data pipelines using AWS S3 and Athena to ensure reliable, consistent datasets for model development and validation.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Identified and eliminated multiple data leakage issues, restructuring feature engineering to enforce strict temporal cutoffs and achieve realistic model accuracy.</t>
+          <t>Implemented tree-based ML models with LightGBM ensembles, combining strong experimentation to achieve stable, realistic forecasts.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Built time-aware validation frameworks simulating production environments, enhancing model credibility and supporting accurate daily country-level remittance volume forecasts.</t>
+          <t>Identified and eliminated data leakage by restructuring feature engineering pipelines with strict temporal validation frameworks.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -652,17 +652,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Specialize in applying statistical and machine learning techniques to model client behavior, churn prediction, and segmentation using unsupervised ML methods.</t>
+          <t>Specialized in statistical modeling and machine learning to analyze client behavior, develop churn and propensity models, and perform client segmentation using unsupervised techniques.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Develop both ad hoc analyses and production-ready predictive models to support business decision-making and forecasting.</t>
+          <t>Skilled in building predictive models and creating production-ready solutions using R, Python, SQL, and Spark (PySpark/Sparklyr).</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Proficient in statistical modeling, hypothesis testing, and machine learning, enabling seamless transition across data science domains including experimentation and visualization.</t>
+          <t>Proficient in hypothesis testing, data visualization, and A/B testing to extract insights and validate data-driven experiments.</t>
         </is>
       </c>
       <c r="L7" t="b">

--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -447,22 +447,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Redesigned client segmentation model using Gaussian Mixture Modeling, applying feature engineering and hypothesis testing to validate new variables.</t>
+          <t>Redesigned client segmentation model using Gaussian Mixture Modeling, feature engineering, and hypothesis testing for accuracy.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Designed and analyzed A/B tests for home page redesign, improving experimental robustness and guiding stakeholder decisions with clear insights.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Developed PySpark data pipelines to process and structure complex accountancy data, enhancing data accessibility and accuracy for financial reporting.</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Mentored junior analysts in statistical methods, experimentation, and machine learning deployment, fostering team analytical capabilities and best practices.</t>
+          <t>Developed PySpark data pipelines to process and analyze accountancy data, improving data accessibility and reliability.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -497,22 +487,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Developed and deployed ML forecasting model predicting promotional sales 21 days ahead, achieving 20% MAPE for FMCG product demand.</t>
+          <t>Developed and deployed an FMCG promotional demand forecasting model achieving 20% MAPE for event sales.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Led creation of ETL pipeline integrating product sales data for supply teams, enabling informed inventory decision-making and forecasting accuracy.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Collaborated with MLOps to deploy daily parallelized sales prediction pipeline using Vertex AI and Kubeflow, reducing process time from 6 hours to 40 minutes.</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Implemented experimental design with causal inference, measuring model impact through hypothesis testing against baseline sales and stock surplus averages.</t>
+          <t>Built an end-to-end ETL pipeline integrating sales data for supply teams, streamlining forecast accessibility.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -547,22 +527,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Developed and deployed forecasting models predicting daily remittance volumes at a country level with 10–15% MAPE across markets.</t>
+          <t>Designed and deployed machine learning models achieving 10% MAPE accuracy for remittance forecasts across countries.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Designed robust data pipelines using AWS S3 and Athena to ensure reliable, consistent datasets for model development and validation.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Implemented tree-based ML models with LightGBM ensembles, combining strong experimentation to achieve stable, realistic forecasts.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Identified and eliminated data leakage by restructuring feature engineering pipelines with strict temporal validation frameworks.</t>
+          <t>Developed forecasting pipeline reducing underfunding daily losses by approximately $500,000 in pilot country.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -652,20 +622,50 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Specialized in statistical modeling and machine learning to analyze client behavior, develop churn and propensity models, and perform client segmentation using unsupervised techniques.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Skilled in building predictive models and creating production-ready solutions using R, Python, SQL, and Spark (PySpark/Sparklyr).</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Proficient in hypothesis testing, data visualization, and A/B testing to extract insights and validate data-driven experiments.</t>
+          <t>Skilled in statistical modeling, machine learning, and predictive analytics for client behavior analysis.</t>
         </is>
       </c>
       <c r="L7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>academic_articles</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Skills &amp; stack</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>BI &amp; Analytics: Looker dashboards, Databricks dashboards, KPI definition and business analytics</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Cloud: Google Cloud Platform (Vertex AI, BigQuery, GCS), AWS (S3, Athena, ECS, ECR, Glue, EventBridge), Databricks</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Data Infrastructure: Athena + S3 data lake, UUID-based data tracking, Prediction + metrics storage systems</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Data Processing: Vectorization and performance optimization, Parallel processing and memory optimization, Large-scale data processing (hundreds of millions of rows)</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Infrastructure: Terraform (IaC), ECS Fargate, EventBridge scheduling</t>
+        </is>
+      </c>
+      <c r="L8" t="b">
         <v>1</v>
       </c>
     </row>

--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -447,22 +447,22 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Redesigned client segmentation model using Gaussian Mixture Modeling, applying feature engineering and hypothesis testing to validate new variables.</t>
+          <t>Redesigned client segmentation using Gaussian Mixture Modeling, applying feature engineering, hypothesis testing, and descriptive statistics for model refinement.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Designed and analyzed A/B tests for home page redesign, improving experimental robustness and guiding stakeholder decisions with clear insights.</t>
+          <t>Led home page redesign experiments, executing A/B testing and reducing click-through rate time by 20%.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Developed PySpark data pipelines to process and structure complex accountancy data, enhancing data accessibility and accuracy for financial reporting.</t>
+          <t>Developed PySpark data pipelines for efficient processing and analysis of accounting data from multiple sources.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Mentored junior analysts in statistical methods, experimentation, and machine learning deployment, fostering team analytical capabilities and best practices.</t>
+          <t>Designed and analyzed randomized experiments to assess customer behavior and model performance metrics.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -497,22 +497,22 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Developed and deployed ML forecasting model predicting promotional sales 21 days ahead, achieving 20% MAPE for FMCG product demand.</t>
+          <t>Developed and deployed a machine learning forecasting model predicting FMCG promotional event sales 21 days ahead with 20% MAPE accuracy.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Led creation of ETL pipeline integrating product sales data for supply teams, enabling informed inventory decision-making and forecasting accuracy.</t>
+          <t>Led creation of automated ETL pipelines integrating sales data into supply team workflows, enhancing data accessibility and orchestration.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Collaborated with MLOps to deploy daily parallelized sales prediction pipeline using Vertex AI and Kubeflow, reducing process time from 6 hours to 40 minutes.</t>
+          <t>Collaborated with ML Operations to deploy daily parallelized sales predictions using Vertex AI and Kubeflow, reducing runtime from 6 hours to 40 minutes.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Implemented experimental design with causal inference, measuring model impact through hypothesis testing against baseline sales and stock surplus averages.</t>
+          <t>Created causal inference experiments and hypothesis testing frameworks to measure model impact, validating $4 million monthly overstock cost savings.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -547,22 +547,22 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Developed and deployed forecasting models predicting daily remittance volumes at a country level with 10–15% MAPE across markets.</t>
+          <t>Developed and deployed an ML forecasting system achieving 10% MAPE accuracy, surpassing manual remittance volume predictions across multiple countries.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Designed robust data pipelines using AWS S3 and Athena to ensure reliable, consistent datasets for model development and validation.</t>
+          <t>Saved approximately $500,000 daily by reducing underfunding via accurate daily liquidity forecasts for a pilot country.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Implemented tree-based ML models with LightGBM ensembles, combining strong experimentation to achieve stable, realistic forecasts.</t>
+          <t>Reduced lockout rates by 25%, decreasing customer disruptions caused by correspondent agents' underfunding through predictive modeling.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Identified and eliminated data leakage by restructuring feature engineering pipelines with strict temporal validation frameworks.</t>
+          <t>Cut remittance prediction processing time from 3 hours to 7 minutes, automating workflows and reducing headcount needs significantly.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -636,36 +636,6 @@
         </is>
       </c>
       <c r="L6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>academic_articles</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Skills &amp; stack</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Specialized in statistical modeling and machine learning to analyze client behavior, develop churn and propensity models, and perform client segmentation using unsupervised techniques.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Skilled in building predictive models and creating production-ready solutions using R, Python, SQL, and Spark (PySpark/Sparklyr).</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Proficient in hypothesis testing, data visualization, and A/B testing to extract insights and validate data-driven experiments.</t>
-        </is>
-      </c>
-      <c r="L7" t="b">
         <v>1</v>
       </c>
     </row>

--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -447,22 +447,22 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Redesigned client segmentation using Gaussian Mixture Modeling, applying feature engineering, hypothesis testing, and descriptive statistics for model refinement.</t>
+          <t>Redesigned and validated client segmentation model using Gaussian Mixture Modeling, descriptive statistics, and hypothesis testing for improved clustering quality.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Led home page redesign experiments, executing A/B testing and reducing click-through rate time by 20%.</t>
+          <t>Analyzed A/B test results and designed experiments to optimize homepage user engagement, reducing click-through rate time by 20%.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Developed PySpark data pipelines for efficient processing and analysis of accounting data from multiple sources.</t>
+          <t>Developed a Pyspark data pipeline to efficiently process and scrutinize financial accountancy data, enhancing data accessibility and reliability.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Designed and analyzed randomized experiments to assess customer behavior and model performance metrics.</t>
+          <t>Built and maintained key performance dashboards using Python, SQL, and Databricks, supporting real-time monitoring of experimentation metrics.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -497,22 +497,22 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Developed and deployed a machine learning forecasting model predicting FMCG promotional event sales 21 days ahead with 20% MAPE accuracy.</t>
+          <t>Developed and deployed a forecasting model predicting promotional FMCG sales 21 days ahead, achieving 20% MAPE accuracy.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Led creation of automated ETL pipelines integrating sales data into supply team workflows, enhancing data accessibility and orchestration.</t>
+          <t>Designed an ETL pipeline and ML workflow that prevented overstock, generating $4 million monthly savings while maintaining sales levels.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Collaborated with ML Operations to deploy daily parallelized sales predictions using Vertex AI and Kubeflow, reducing runtime from 6 hours to 40 minutes.</t>
+          <t>Collaborated with MLOps to deploy parallelized sales prediction pipelines on Vertex AI and Kubeflow, reducing runtime from 6 hours to 40 minutes.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Created causal inference experiments and hypothesis testing frameworks to measure model impact, validating $4 million monthly overstock cost savings.</t>
+          <t>Built a model performance database to monitor KPIs, track bugs, and communicate statistical robustness and forecast reliability to stakeholders.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -547,22 +547,22 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Developed and deployed an ML forecasting system achieving 10% MAPE accuracy, surpassing manual remittance volume predictions across multiple countries.</t>
+          <t>Developed and deployed ML forecasting models predicting daily remittance volumes at country level with 10% MAPE accuracy.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Saved approximately $500,000 daily by reducing underfunding via accurate daily liquidity forecasts for a pilot country.</t>
+          <t>Streamlined data pipelines using AWS S3, Athena, and containerized environments to ensure reliable, scalable production predictions.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Reduced lockout rates by 25%, decreasing customer disruptions caused by correspondent agents' underfunding through predictive modeling.</t>
+          <t>Saved approximately $500,000 daily by reducing underfunding in pilot country through automated, data-driven liquidity planning models.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Cut remittance prediction processing time from 3 hours to 7 minutes, automating workflows and reducing headcount needs significantly.</t>
+          <t>Reduced correspondent agent lockout rates by 25% via improved prediction models, increasing transaction success and customer satisfaction.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -636,6 +636,36 @@
         </is>
       </c>
       <c r="L6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>skills_stack</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Skills &amp; stack</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Statistical modeling, causal inference, price elasticity, marketing mix modelling expertise</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Python, SQL, cloud platforms (AWS, GCP), ML deployment, MLOps tools (Kubeflow, Docker, CI/CD)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Data visualization (Power BI, Looker), stakeholder communication, FMCG domain knowledge, mentoring</t>
+        </is>
+      </c>
+      <c r="L7" t="b">
         <v>1</v>
       </c>
     </row>

--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -447,22 +447,22 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Redesigned and validated client segmentation model using Gaussian Mixture Modeling, descriptive statistics, and hypothesis testing for improved clustering quality.</t>
+          <t>Redesigned client segmentation model using Gaussian Mixture Modeling, feature engineering, and hypothesis testing to improve customer clustering accuracy.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Analyzed A/B test results and designed experiments to optimize homepage user engagement, reducing click-through rate time by 20%.</t>
+          <t>Developed and maintained performance dashboards tracking key metrics, supporting data-driven decision making within the experimentation team.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Developed a Pyspark data pipeline to efficiently process and scrutinize financial accountancy data, enhancing data accessibility and reliability.</t>
+          <t>Led design and analysis of A/B tests on homepage redesign, achieving a 20% reduction in user click-through time.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Built and maintained key performance dashboards using Python, SQL, and Databricks, supporting real-time monitoring of experimentation metrics.</t>
+          <t>Built PySpark data pipelines to process and analyze large-scale accountancy and transactional datasets for financial reporting and operational insights.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -497,22 +497,22 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Developed and deployed a forecasting model predicting promotional FMCG sales 21 days ahead, achieving 20% MAPE accuracy.</t>
+          <t>Developed an end-to-end forecasting model predicting FMCG promotional sales 21 days ahead, achieving 20% MAPE accuracy and $4 million monthly savings.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Designed an ETL pipeline and ML workflow that prevented overstock, generating $4 million monthly savings while maintaining sales levels.</t>
+          <t>Designed and deployed a scalable, parallelized ETL pipeline and ML workflow using Vertex AI and Kubeflow Pipelines, reducing runtime from 6 hours to 40 minutes.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Collaborated with MLOps to deploy parallelized sales prediction pipelines on Vertex AI and Kubeflow, reducing runtime from 6 hours to 40 minutes.</t>
+          <t>Established causal inference methodology and experimental design to measure model impact, validating results with hypothesis testing and comparative baseline analysis.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Built a model performance database to monitor KPIs, track bugs, and communicate statistical robustness and forecast reliability to stakeholders.</t>
+          <t>Created and managed a performance monitoring database to track model KPIs, detect bugs, and support continuous improvement efforts.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -547,22 +547,22 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Developed and deployed ML forecasting models predicting daily remittance volumes at country level with 10% MAPE accuracy.</t>
+          <t>Developed a production-grade forecasting model predicting daily remittance volumes with 10% MAPE accuracy, surpassing manual methods.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Streamlined data pipelines using AWS S3, Athena, and containerized environments to ensure reliable, scalable production predictions.</t>
+          <t>Saved approximately $500,000 daily by reducing underfunding in pilot country, significantly improving capital allocation efficiency.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Saved approximately $500,000 daily by reducing underfunding in pilot country through automated, data-driven liquidity planning models.</t>
+          <t>Decreased lockout rates by 25% compared to manual processes, reducing customer blocking due to correspondent agent underfunding.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Reduced correspondent agent lockout rates by 25% via improved prediction models, increasing transaction success and customer satisfaction.</t>
+          <t>Reduced remittance prediction processing time from 3 hours to 7 minutes through automation, saving human resources and accelerating decision-making.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -652,17 +652,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Statistical modeling, causal inference, price elasticity, marketing mix modelling expertise</t>
+          <t>Python, SQL, machine learning (LightGBM, logistic regression), statistical modeling, predictive analytics</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Python, SQL, cloud platforms (AWS, GCP), ML deployment, MLOps tools (Kubeflow, Docker, CI/CD)</t>
+          <t>Cloud platforms and MLOps: AWS, GCP (Vertex AI, BigQuery), Docker, Kubeflow, CI/CD with GitHub Actions</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Data visualization (Power BI, Looker), stakeholder communication, FMCG domain knowledge, mentoring</t>
+          <t>Price elasticity, marketing mix modelling, experimentation design, Power BI, stakeholder communication, FMCG mentoring</t>
         </is>
       </c>
       <c r="L7" t="b">

--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -447,22 +447,22 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Redesigned client segmentation model using Gaussian Mixture Modeling, feature engineering, and hypothesis testing to improve customer clustering accuracy.</t>
+          <t>Redesigned client segmentation model using Gaussian Mixture Modeling, enhancing feature engineering and statistical validation for improved customer clustering.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Developed and maintained performance dashboards tracking key metrics, supporting data-driven decision making within the experimentation team.</t>
+          <t>Designed and analyzed A/B tests for home page redesign, achieving a 20% reduction in click-through rate time to boost engagement.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Led design and analysis of A/B tests on homepage redesign, achieving a 20% reduction in user click-through time.</t>
+          <t>Developed data pipelines with PySpark to process and analyze complex accountancy data, improving data accessibility and reliability.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Built PySpark data pipelines to process and analyze large-scale accountancy and transactional datasets for financial reporting and operational insights.</t>
+          <t>Built and maintained performance dashboards using Python, R, and SQL, providing clear metrics to support squad decision-making.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -497,22 +497,22 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Developed an end-to-end forecasting model predicting FMCG promotional sales 21 days ahead, achieving 20% MAPE accuracy and $4 million monthly savings.</t>
+          <t>Developed and deployed a machine learning forecasting model with 20% MAPE accuracy for FMCG promotional event sales, predicting 21 days ahead.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Designed and deployed a scalable, parallelized ETL pipeline and ML workflow using Vertex AI and Kubeflow Pipelines, reducing runtime from 6 hours to 40 minutes.</t>
+          <t>Led creation of an ETL pipeline integrating sales data for supply teams, enabling real-time demand forecasting and inventory management.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Established causal inference methodology and experimental design to measure model impact, validating results with hypothesis testing and comparative baseline analysis.</t>
+          <t>Collaborated with MLOps team to deploy daily parallelized sales prediction pipelines using Vertex AI and Kubeflow, reducing runtime from 6 hours to 40 minutes.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Created and managed a performance monitoring database to track model KPIs, detect bugs, and support continuous improvement efforts.</t>
+          <t>Implemented causal inference experimental design to measure model impact on sales and stock, ensuring robust hypothesis testing and validation.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -547,22 +547,22 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Developed a production-grade forecasting model predicting daily remittance volumes with 10% MAPE accuracy, surpassing manual methods.</t>
+          <t>Developed a production forecasting system predicting daily remittance volumes with 10% MAPE, outperforming manual methods consistently.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Saved approximately $500,000 daily by reducing underfunding in pilot country, significantly improving capital allocation efficiency.</t>
+          <t>Built robust ML pipelines using LightGBM and ensemble models with time-aware validation to ensure realistic, leak-free forecasts.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Decreased lockout rates by 25% compared to manual processes, reducing customer blocking due to correspondent agent underfunding.</t>
+          <t>Saved approximately $500,000 daily by reducing underfunding in pilot country through accurate remittance volume predictions.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Reduced remittance prediction processing time from 3 hours to 7 minutes through automation, saving human resources and accelerating decision-making.</t>
+          <t>Reduced lockout rates by 25% compared to manual process, increasing customer access and reducing financial service disruptions.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -652,17 +652,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Python, SQL, machine learning (LightGBM, logistic regression), statistical modeling, predictive analytics</t>
+          <t>Python, SQL, R for statistical modeling, machine learning, and data analysis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Cloud platforms and MLOps: AWS, GCP (Vertex AI, BigQuery), Docker, Kubeflow, CI/CD with GitHub Actions</t>
+          <t>Cloud platforms (AWS, GCP) and MLOps (Kubeflow, Docker, CI/CD) for scalable model deployment</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Price elasticity, marketing mix modelling, experimentation design, Power BI, stakeholder communication, FMCG mentoring</t>
+          <t>Marketing mix modeling, price elasticity, experimentation, and eCommerce analytics with visualization tools</t>
         </is>
       </c>
       <c r="L7" t="b">

--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -447,22 +447,22 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Redesigned client segmentation model using Gaussian Mixture Modeling, enhancing feature engineering and statistical validation for improved customer clustering.</t>
+          <t>Redesigned client segmentation model using feature engineering and hypothesis testing to improve customer behavior insights and segmentation accuracy.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Designed and analyzed A/B tests for home page redesign, achieving a 20% reduction in click-through rate time to boost engagement.</t>
+          <t>Led A/B test experimental design and analysis for home page, achieving a 20% reduction in click-through rate time.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Developed data pipelines with PySpark to process and analyze complex accountancy data, improving data accessibility and reliability.</t>
+          <t>Developed and maintained key results dashboard to monitor team performance metrics for experimentation and client behavior projects.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Built and maintained performance dashboards using Python, R, and SQL, providing clear metrics to support squad decision-making.</t>
+          <t>Built data pipelines with PySpark to automate extraction and processing of accountancy and customer transaction data efficiently.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -497,22 +497,22 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Developed and deployed a machine learning forecasting model with 20% MAPE accuracy for FMCG promotional event sales, predicting 21 days ahead.</t>
+          <t>Developed an end-to-end forecasting model for FMCG promotional events, achieving 20% MAPE and predicting sales 21 days in advance.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Led creation of an ETL pipeline integrating sales data for supply teams, enabling real-time demand forecasting and inventory management.</t>
+          <t>Designed and implemented an ETL pipeline to consolidate product sales data, enabling daily parallel training of store-specific sales models.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Collaborated with MLOps team to deploy daily parallelized sales prediction pipelines using Vertex AI and Kubeflow, reducing runtime from 6 hours to 40 minutes.</t>
+          <t>Collaborated on model deployment using Vertex AI and Kubeflow, reducing processing time from 6 hours to 40 minutes via code optimization.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Implemented causal inference experimental design to measure model impact on sales and stock, ensuring robust hypothesis testing and validation.</t>
+          <t>Led causal inference experiments comparing model-driven sales and stock data, validating impact and generating $4 million monthly overstock savings.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -547,22 +547,22 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Developed a production forecasting system predicting daily remittance volumes with 10% MAPE, outperforming manual methods consistently.</t>
+          <t>Developed a production-grade forecasting system predicting daily remittance volumes with 10% MAPE, improving accuracy over manual methods.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Built robust ML pipelines using LightGBM and ensemble models with time-aware validation to ensure realistic, leak-free forecasts.</t>
+          <t>Designed robust data pipelines integrating AWS S3 and Athena, ensuring reliable datasets for modeling and validation at scale.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Saved approximately $500,000 daily by reducing underfunding in pilot country through accurate remittance volume predictions.</t>
+          <t>Built machine learning models using LightGBM ensembles with strict temporal validation to prevent data leakage and ensure realistic performance.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Reduced lockout rates by 25% compared to manual process, increasing customer access and reducing financial service disruptions.</t>
+          <t>Achieved approximately $500,000 daily savings by reducing underfunding in the pilot country’s remittance liquidity planning process.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -652,17 +652,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Python, SQL, R for statistical modeling, machine learning, and data analysis</t>
+          <t>Python programming with pandas, NumPy, scikit-learn, Keras, TensorFlow, and PyTorch for...</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Cloud platforms (AWS, GCP) and MLOps (Kubeflow, Docker, CI/CD) for scalable model deployment</t>
+          <t>SQL and data manipulation for large-scale data processing and exploratory analysis</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Marketing mix modeling, price elasticity, experimentation, and eCommerce analytics with visualization tools</t>
+          <t>AWS, Azure, GCP cloud platforms, Git version control, model deployment, automation, and...</t>
         </is>
       </c>
       <c r="L7" t="b">

--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -447,22 +447,22 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Redesigned client segmentation model using feature engineering and hypothesis testing to improve customer behavior insights and segmentation accuracy.</t>
+          <t>Developed and maintained scalable data pipelines in PySpark to process and analyze large-scale accountancy and customer transaction datasets.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Led A/B test experimental design and analysis for home page, achieving a 20% reduction in click-through rate time.</t>
+          <t>Redesigned client segmentation using Gaussian Mixture Models, applying feature engineering and statistical validation to improve model accuracy.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Developed and maintained key results dashboard to monitor team performance metrics for experimentation and client behavior projects.</t>
+          <t>Led A/B testing and experimental design to evaluate homepage redesign, achieving a 20% reduction in click-through rate time.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Built data pipelines with PySpark to automate extraction and processing of accountancy and customer transaction data efficiently.</t>
+          <t>Created and managed performance dashboards tracking key metrics to support data-driven decisions and team project evaluations.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -497,22 +497,22 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Developed an end-to-end forecasting model for FMCG promotional events, achieving 20% MAPE and predicting sales 21 days in advance.</t>
+          <t>Developed and deployed a forecasting model predicting promotional sales with 20% MAPE, enhancing FMCG event sales predictability.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Designed and implemented an ETL pipeline to consolidate product sales data, enabling daily parallel training of store-specific sales models.</t>
+          <t>Created an end-to-end ETL pipeline enabling daily, parallelized sales forecasts for individual stores using Vertex AI and Kubeflow Pipelines.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Collaborated on model deployment using Vertex AI and Kubeflow, reducing processing time from 6 hours to 40 minutes via code optimization.</t>
+          <t>Optimized model training pipeline, reducing process time from 6 hours to 40 minutes through code vectorization and transition from pandas to polars.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Led causal inference experiments comparing model-driven sales and stock data, validating impact and generating $4 million monthly overstock savings.</t>
+          <t>Implemented causal inference methodology and experimental design to measure model impact, achieving $4 million monthly savings by preventing overstock.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -547,22 +547,22 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Developed a production-grade forecasting system predicting daily remittance volumes with 10% MAPE, improving accuracy over manual methods.</t>
+          <t>Developed a production-grade forecasting system predicting daily remittance volumes with 10% MAPE accuracy, improving capital allocation decisions.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Designed robust data pipelines integrating AWS S3 and Athena, ensuring reliable datasets for modeling and validation at scale.</t>
+          <t>Designed and automated a data pipeline integrating AWS S3 and Athena sources, ensuring reliable datasets for scalable machine learning deployment.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Built machine learning models using LightGBM ensembles with strict temporal validation to prevent data leakage and ensure realistic performance.</t>
+          <t>Implemented LightGBM and ensemble models combined with time-aware validation to simulate real production behavior and prevent data leakage.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Achieved approximately $500,000 daily savings by reducing underfunding in the pilot country’s remittance liquidity planning process.</t>
+          <t>Reduced remittance prediction processing time from 3 hours to 7 minutes, significantly lowering manual workload and operational costs.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -652,17 +652,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Python programming with pandas, NumPy, scikit-learn, Keras, TensorFlow, and PyTorch for...</t>
+          <t>Python, SQL, pandas, NumPy, scikit-learn, Keras, TensorFlow, PyTorch for ML modeling an...</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SQL and data manipulation for large-scale data processing and exploratory analysis</t>
+          <t>AWS, Azure, GCP, Docker, Kubernetes, Kubeflow, CI/CD pipelines, Git for cloud, containe...</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP cloud platforms, Git version control, model deployment, automation, and...</t>
+          <t>Machine learning algorithms, statistical methods, Spark, Hadoop, model deployment, end-...</t>
         </is>
       </c>
       <c r="L7" t="b">

--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -447,22 +447,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Developed and maintained scalable data pipelines in PySpark to process and analyze large-scale accountancy and customer transaction datasets.</t>
+          <t>Recreated and validated client segmentation model using Gaussian Mixture Modeling, descriptive statistics, and feature engineering for improved clustering accuracy.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Redesigned client segmentation using Gaussian Mixture Models, applying feature engineering and statistical validation to improve model accuracy.</t>
+          <t>Designed and analyzed A/B tests for the home page, achieving a 20% reduction in click-through rate time metric.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Led A/B testing and experimental design to evaluate homepage redesign, achieving a 20% reduction in click-through rate time.</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Created and managed performance dashboards tracking key metrics to support data-driven decisions and team project evaluations.</t>
+          <t>Developed and maintained performance dashboards to monitor key results and support data-driven decision-making for experimentation teams.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -497,22 +492,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Developed and deployed a forecasting model predicting promotional sales with 20% MAPE, enhancing FMCG event sales predictability.</t>
+          <t>Developed an end-to-end forecasting model predicting promotional sales for FMCG with 20% MAPE, improving event sales predictability.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Created an end-to-end ETL pipeline enabling daily, parallelized sales forecasts for individual stores using Vertex AI and Kubeflow Pipelines.</t>
+          <t>Delivered automated daily predictions for each store using parallelized pipelines on Vertex AI, reducing process time from 6 hours to 40 minutes.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Optimized model training pipeline, reducing process time from 6 hours to 40 minutes through code vectorization and transition from pandas to polars.</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Implemented causal inference methodology and experimental design to measure model impact, achieving $4 million monthly savings by preventing overstock.</t>
+          <t>Implemented an orchestrated ETL pipeline aggregating sales data, enabling supply teams to access clean, reliable data for decision making.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -547,22 +537,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Developed a production-grade forecasting system predicting daily remittance volumes with 10% MAPE accuracy, improving capital allocation decisions.</t>
+          <t>Developed production-grade forecasting system predicting daily remittance volumes with 10% MAPE, surpassing manual process accuracy.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Designed and automated a data pipeline integrating AWS S3 and Athena sources, ensuring reliable datasets for scalable machine learning deployment.</t>
+          <t>Engineered robust AWS data pipeline using S3 and Athena, ensuring reliable datasets for machine learning model training and validation.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Implemented LightGBM and ensemble models combined with time-aware validation to simulate real production behavior and prevent data leakage.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Reduced remittance prediction processing time from 3 hours to 7 minutes, significantly lowering manual workload and operational costs.</t>
+          <t>Implemented tree-based LightGBM models with time-aware validation, improving forecast stability and preventing data leakage in feature engineering.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -652,17 +637,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Python, SQL, pandas, NumPy, scikit-learn, Keras, TensorFlow, PyTorch for ML modeling an...</t>
+          <t>Python programming with pandas, NumPy, scikit-learn, TensorFlow, Keras, PyTorch for mac...</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Docker, Kubernetes, Kubeflow, CI/CD pipelines, Git for cloud, containe...</t>
+          <t>SQL for data querying and modeling; AWS, Azure, GCP cloud platforms for model deploymen...</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Machine learning algorithms, statistical methods, Spark, Hadoop, model deployment, end-...</t>
+          <t>Git version control, collaborative communication, end-to-end ML system ownership, stron...</t>
         </is>
       </c>
       <c r="L7" t="b">

--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -447,17 +447,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Recreated and validated client segmentation model using Gaussian Mixture Modeling, descriptive statistics, and feature engineering for improved clustering accuracy.</t>
+          <t>Recreated PicPay's client segmentation model using Gaussian Mixture Modeling, feature engineering, and hypothesis testing to improve clustering accuracy.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Designed and analyzed A/B tests for the home page, achieving a 20% reduction in click-through rate time metric.</t>
+          <t>Led home page redesign efforts, conducting A/B tests that reduced click-through rate time by 20%, enhancing user engagement insights.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Developed and maintained performance dashboards to monitor key results and support data-driven decision-making for experimentation teams.</t>
+          <t>Developed a PySpark data pipeline to efficiently analyze and validate accountancy data, improving data accessibility and reporting accuracy.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -492,17 +492,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Developed an end-to-end forecasting model predicting promotional sales for FMCG with 20% MAPE, improving event sales predictability.</t>
+          <t>Developed an end-to-end forecasting workflow for promotional demand, improving predictability with 20% MAPE for FMCG sales forecasts.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Delivered automated daily predictions for each store using parallelized pipelines on Vertex AI, reducing process time from 6 hours to 40 minutes.</t>
+          <t>Designed and deployed parallelized daily sales prediction pipelines using Vertex AI and Kubeflow, reducing runtime from 6 hours to 40 minutes.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Implemented an orchestrated ETL pipeline aggregating sales data, enabling supply teams to access clean, reliable data for decision making.</t>
+          <t>Created a performance database to monitor model KPIs and track bugs, enabling continuous evaluation and improvement of forecasting accuracy.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -537,17 +537,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Developed production-grade forecasting system predicting daily remittance volumes with 10% MAPE, surpassing manual process accuracy.</t>
+          <t>Developed a production-grade forecasting system predicting daily remittance volumes with 10% MAPE, surpassing manual process accuracy.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Engineered robust AWS data pipeline using S3 and Athena, ensuring reliable datasets for machine learning model training and validation.</t>
+          <t>Designed and implemented data pipelines integrating AWS S3 and Athena, ensuring consistent datasets for reliable model training and validation.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Implemented tree-based LightGBM models with time-aware validation, improving forecast stability and preventing data leakage in feature engineering.</t>
+          <t>Built machine learning models using LightGBM and ensemble methods with time-aware validation, eliminating data leakage and ensuring temporal consistency.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -632,25 +632,115 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Skills &amp; stack</t>
+          <t>BI &amp; Analytics</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Python programming with pandas, NumPy, scikit-learn, TensorFlow, Keras, PyTorch for mac...</t>
+          <t>Looker dashboards for interactive data visualization and business insights.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SQL for data querying and modeling; AWS, Azure, GCP cloud platforms for model deploymen...</t>
+          <t>Databricks dashboards to monitor KPIs and drive data-driven decisions.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Git version control, collaborative communication, end-to-end ML system ownership, stron...</t>
+          <t>Define KPIs and conduct business analytics to measure performance effectively.</t>
         </is>
       </c>
       <c r="L7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>skills_stack</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Google Cloud Platform tools: Vertex AI, BigQuery, and Google Cloud Storage (GCS) for scalable data solutions</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>AWS services: S3, Athena, ECS, ECR, Glue, and EventBridge for data storage, querying, and orchestration</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Databricks platform for integrated data engineering, exploration, and analytics workflows</t>
+        </is>
+      </c>
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>skills_stack</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Data Infrastructure</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Experience with Athena and S3 for efficient data lake querying and storage management.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Implemented UUID-based data tracking to ensure data integrity and traceability.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Developed prediction and metrics storage systems to support scalable machine learning workflows.</t>
+        </is>
+      </c>
+      <c r="L9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>skills_stack</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Data Processing</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Optimized data workflows using vectorization for enhanced performance and scalability</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Implemented parallel processing techniques to improve memory and computation efficiency</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Handled large-scale data processing tasks involving hundreds of millions of rows effectively</t>
+        </is>
+      </c>
+      <c r="L10" t="b">
         <v>1</v>
       </c>
     </row>

--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -447,17 +447,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Recreated PicPay's client segmentation model using Gaussian Mixture Modeling, feature engineering, and hypothesis testing to improve clustering accuracy.</t>
+          <t>Recreated and validated client segmentation model using descriptive statistics, hypothesis testing, and feature engineering to improve clustering accuracy.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Led home page redesign efforts, conducting A/B tests that reduced click-through rate time by 20%, enhancing user engagement insights.</t>
+          <t>Led analysis and design of A/B experiments to evaluate homepage redesign, achieving a 20% reduction in click-through rate time.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Developed a PySpark data pipeline to efficiently analyze and validate accountancy data, improving data accessibility and reporting accuracy.</t>
+          <t>Developed and maintained key performance dashboards for monitoring team metrics and supporting data-driven decision making.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -492,17 +492,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Developed an end-to-end forecasting workflow for promotional demand, improving predictability with 20% MAPE for FMCG sales forecasts.</t>
+          <t>Developed and deployed an end-to-end forecasting model for FMCG promotional events, achieving 20% MAPE and $4 million monthly savings by preventing overstock.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Designed and deployed parallelized daily sales prediction pipelines using Vertex AI and Kubeflow, reducing runtime from 6 hours to 40 minutes.</t>
+          <t>Designed and implemented a clean ETL pipeline to provide daily sales data, facilitating accurate demand forecasting and seamless ERP integration for supply teams.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Created a performance database to monitor model KPIs and track bugs, enabling continuous evaluation and improvement of forecasting accuracy.</t>
+          <t>Collaborated with MLOps team to optimize code and deploy parallelized pipelines on Vertex AI, reducing daily prediction runtime from 6 hours to 40 minutes.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -537,17 +537,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Developed a production-grade forecasting system predicting daily remittance volumes with 10% MAPE, surpassing manual process accuracy.</t>
+          <t>Designed and deployed machine learning forecasting system predicting daily remittance volumes with 10% MAPE, outperforming manual methods.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Designed and implemented data pipelines integrating AWS S3 and Athena, ensuring consistent datasets for reliable model training and validation.</t>
+          <t>Implemented automated data pipeline integrating AWS S3 and Athena, ensuring consistent, reliable datasets for modeling and production use.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Built machine learning models using LightGBM and ensemble methods with time-aware validation, eliminating data leakage and ensuring temporal consistency.</t>
+          <t>Developed LightGBM ensemble models incorporating temporal validation, preventing data leakage and enhancing model stability for multiple countries.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -637,17 +637,27 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Looker dashboards for interactive data visualization and business insights.</t>
+          <t>Developed and maintained Looker dashboards for business performance monitoring.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Databricks dashboards to monitor KPIs and drive data-driven decisions.</t>
+          <t>Designed KPI definitions to align analytics with organizational goals.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Define KPIs and conduct business analytics to measure performance effectively.</t>
+          <t>Created interactive Databricks dashboards to visualize key metrics.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Conducted business analytics to identify trends and support decision-making.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Collaborated with teams to translate data insights into actionable strategies.</t>
         </is>
       </c>
       <c r="L7" t="b">
@@ -667,17 +677,27 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Google Cloud Platform tools: Vertex AI, BigQuery, and Google Cloud Storage (GCS) for scalable data solutions</t>
+          <t>AWS cloud services including S3, Athena, ECS, ECR, Glue, and EventBridge</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>AWS services: S3, Athena, ECS, ECR, Glue, and EventBridge for data storage, querying, and orchestration</t>
+          <t>Google Cloud Platform tools such as Vertex AI, BigQuery, and Google Cloud Storage</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Databricks platform for integrated data engineering, exploration, and analytics workflows</t>
+          <t>Databricks platform for data engineering and collaborative analytics</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Cloud-based data storage, processing, and automated event management</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Integration of cloud services for scalable machine learning model deployment</t>
         </is>
       </c>
       <c r="L8" t="b">
@@ -697,17 +717,27 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Experience with Athena and S3 for efficient data lake querying and storage management.</t>
+          <t>Athena and S3 for scalable data lake querying and storage optimization.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Implemented UUID-based data tracking to ensure data integrity and traceability.</t>
+          <t>UUID-based data tracking for consistent and reliable data identification.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Developed prediction and metrics storage systems to support scalable machine learning workflows.</t>
+          <t>Design and implement prediction storage systems for ML model outputs.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Develop metrics storage architectures to monitor and evaluate model performance.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Integrate Prediction and metrics systems to support automated model evaluation.</t>
         </is>
       </c>
       <c r="L9" t="b">
@@ -727,20 +757,70 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Optimized data workflows using vectorization for enhanced performance and scalability</t>
+          <t>Vectorization techniques for optimized data processing and analysis workflows</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Implemented parallel processing techniques to improve memory and computation efficiency</t>
+          <t>Parallel processing to enhance computational efficiency in data tasks</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Handled large-scale data processing tasks involving hundreds of millions of rows effectively</t>
+          <t>Memory optimization strategies for handling complex datasets efficiently</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Large-scale data processing of hundreds of millions of rows with performance focus</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Efficient use of system resources for scalable data manipulation and computation</t>
         </is>
       </c>
       <c r="L10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>skills_stack</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Infrastructure as Code using Terraform for automated cloud resource management</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Deployment and orchestration with ECS Fargate for containerized applications</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Event-driven architecture using AWS EventBridge for scheduling and event management</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Image storage and management with Amazon ECR container registry</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Cloud infrastructure automation focusing on reliability and scalability</t>
+        </is>
+      </c>
+      <c r="L11" t="b">
         <v>1</v>
       </c>
     </row>

--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -447,17 +447,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Recreated and validated client segmentation model using descriptive statistics, hypothesis testing, and feature engineering to improve clustering accuracy.</t>
+          <t>Recreated client segmentation using Gaussian Mixture Modeling, feature engineering, and hypothesis testing to improve clustering accuracy and insights.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Led analysis and design of A/B experiments to evaluate homepage redesign, achieving a 20% reduction in click-through rate time.</t>
+          <t>Led design and analysis of A/B experiments for home page redesign, reducing click-through rate time by 20%.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Developed and maintained key performance dashboards for monitoring team metrics and supporting data-driven decision making.</t>
+          <t>Developed and maintained a key performance metric dashboard using SQL, Python, and Databricks notebooks for real-time monitoring.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -492,17 +492,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Developed and deployed an end-to-end forecasting model for FMCG promotional events, achieving 20% MAPE and $4 million monthly savings by preventing overstock.</t>
+          <t>Developed and deployed an ML forecasting model improving FMCG event sales predictability with 20% MAPE, aiding supply chain teams.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Designed and implemented a clean ETL pipeline to provide daily sales data, facilitating accurate demand forecasting and seamless ERP integration for supply teams.</t>
+          <t>Built an end-to-end ETL pipeline and parallelized daily sales prediction models using Vertex AI and Kubeflow Pipelines for faster insights.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Collaborated with MLOps team to optimize code and deploy parallelized pipelines on Vertex AI, reducing daily prediction runtime from 6 hours to 40 minutes.</t>
+          <t>Optimized pipeline code by converting pandas to polars, reducing processing time from 6 hours to 40 minutes for multiple store models.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -537,17 +537,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Designed and deployed machine learning forecasting system predicting daily remittance volumes with 10% MAPE, outperforming manual methods.</t>
+          <t>Developed and deployed ML forecasting models achieving 10% MAPE, surpassing manual prediction accuracy for multiple country-level remittance volumes.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Implemented automated data pipeline integrating AWS S3 and Athena, ensuring consistent, reliable datasets for modeling and production use.</t>
+          <t>Designed and implemented AWS-based data pipelines using S3 and Athena, ensuring reliable data integration and timely model updates daily.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Developed LightGBM ensemble models incorporating temporal validation, preventing data leakage and enhancing model stability for multiple countries.</t>
+          <t>Reduced daily underfunding by approximately $500,000 and cut lockout rates by 25% compared to manual liquidity planning processes.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -637,27 +637,27 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Developed and maintained Looker dashboards for business performance monitoring.</t>
+          <t>Databricks dashboards for real-time data visualization and business analytics insights.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Designed KPI definitions to align analytics with organizational goals.</t>
+          <t>Looker dashboards to create interactive KPI tracking and performance monitoring.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Created interactive Databricks dashboards to visualize key metrics.</t>
+          <t>Defining and analyzing KPIs using Looker and Databricks for data-driven decision-making.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Conducted business analytics to identify trends and support decision-making.</t>
+          <t>Building business analytics reports integrating Databricks and Looker platforms.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Collaborated with teams to translate data insights into actionable strategies.</t>
+          <t>Translating complex data into actionable insights with Databricks and Looker dashboards.</t>
         </is>
       </c>
       <c r="L7" t="b">
@@ -677,27 +677,27 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AWS cloud services including S3, Athena, ECS, ECR, Glue, and EventBridge</t>
+          <t>Google Cloud Platform with Vertex AI for managed machine learning workflows and BigQuery for analytics</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Google Cloud Platform tools such as Vertex AI, BigQuery, and Google Cloud Storage</t>
+          <t>AWS services including S3 for storage, Athena for SQL querying, and Glue for ETL pipelines</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Databricks platform for data engineering and collaborative analytics</t>
+          <t>Databricks platform for collaborative data engineering and scalable machine learning model development</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Cloud-based data storage, processing, and automated event management</t>
+          <t>AWS ECS and ECR for containerized ML model deployment and orchestration</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Integration of cloud services for scalable machine learning model deployment</t>
+          <t>EventBridge for event-driven integration supporting automated ML pipeline triggers</t>
         </is>
       </c>
       <c r="L8" t="b">
@@ -717,27 +717,27 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Athena and S3 for scalable data lake querying and storage optimization.</t>
+          <t>Athena and S3 data lake for scalable data storage and query execution.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>UUID-based data tracking for consistent and reliable data identification.</t>
+          <t>UUID-based data tracking to ensure data integrity and lineage.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Design and implement prediction storage systems for ML model outputs.</t>
+          <t>Prediction storage systems for maintaining model outputs and metrics.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Develop metrics storage architectures to monitor and evaluate model performance.</t>
+          <t>Metrics storage systems supporting performance monitoring and analysis.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Integrate Prediction and metrics systems to support automated model evaluation.</t>
+          <t>Integrated data infrastructure leveraging Athena and S3 for advanced analytics.</t>
         </is>
       </c>
       <c r="L9" t="b">
@@ -757,27 +757,27 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Vectorization techniques for optimized data processing and analysis workflows</t>
+          <t>Vectorization techniques for optimized Python numerical computations and data handling</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Parallel processing to enhance computational efficiency in data tasks</t>
+          <t>Performance optimization using memory-efficient data structures and algorithms</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Memory optimization strategies for handling complex datasets efficiently</t>
+          <t>Parallel processing methods to accelerate data workflows and model training</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Large-scale data processing of hundreds of millions of rows with performance focus</t>
+          <t>Handling large-scale data processing with expertise in datasets of hundreds of millions of rows</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Efficient use of system resources for scalable data manipulation and computation</t>
+          <t>Applying advanced vectorization and parallelization for scalable machine learning pipelines</t>
         </is>
       </c>
       <c r="L10" t="b">
@@ -797,27 +797,27 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Infrastructure as Code using Terraform for automated cloud resource management</t>
+          <t>Terraform for infrastructure as code and automated provisioning in cloud environments</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Deployment and orchestration with ECS Fargate for containerized applications</t>
+          <t>ECS Fargate for scalable container deployment and orchestration</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Event-driven architecture using AWS EventBridge for scheduling and event management</t>
+          <t>EventBridge scheduling to automate event-driven workflows and task execution</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Image storage and management with Amazon ECR container registry</t>
+          <t>ECR image registry for secure container image storage and management</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Cloud infrastructure automation focusing on reliability and scalability</t>
+          <t>Integrated Terraform with ECS Fargate and ECR for streamlined ML model deployment pipelines</t>
         </is>
       </c>
       <c r="L11" t="b">

--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -427,37 +427,37 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PicPay</t>
+          <t>Melhor Envio</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Recreated client segmentation using Gaussian Mixture Modeling, feature engineering, and hypothesis testing to improve clustering accuracy and insights.</t>
+          <t>Developed unsupervised client segmentation model using K-prototypes, enabling targeted coupon campaigns that increased conversion rates by 20%.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Led design and analysis of A/B experiments for home page redesign, reducing click-through rate time by 20%.</t>
+          <t>Created real-time client activity monitoring system that identified churn risk, enabling timely interventions to reduce overall client attrition.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Developed and maintained a key performance metric dashboard using SQL, Python, and Databricks notebooks for real-time monitoring.</t>
+          <t>Designed and implemented an activity status data pipeline, improving client maturity insights and supporting strategic engagement decisions.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -492,17 +492,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Developed and deployed an ML forecasting model improving FMCG event sales predictability with 20% MAPE, aiding supply chain teams.</t>
+          <t>Developed and deployed a forecasting model for promotional FMCG sales, achieving 20% MAPE and enabling 21-day advance predictions.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Built an end-to-end ETL pipeline and parallelized daily sales prediction models using Vertex AI and Kubeflow Pipelines for faster insights.</t>
+          <t>Designed an ETL pipeline integrating sales data, facilitating daily parallel model training for each store and improving data availability.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Optimized pipeline code by converting pandas to polars, reducing processing time from 6 hours to 40 minutes for multiple store models.</t>
+          <t>Collaborated with MLOps team to deploy sales prediction pipelines on Vertex AI using Kubeflow, reducing processing time from 6 hours to 40 minutes.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -537,17 +537,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Developed and deployed ML forecasting models achieving 10% MAPE, surpassing manual prediction accuracy for multiple country-level remittance volumes.</t>
+          <t>Developed a machine learning forecasting system achieving 10% MAPE across countries, outperforming prior manual liquidity planning methods.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Designed and implemented AWS-based data pipelines using S3 and Athena, ensuring reliable data integration and timely model updates daily.</t>
+          <t>Saved around $500,000 daily by reducing underfunding in a pilot country through accurate remittance volume predictions.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Reduced daily underfunding by approximately $500,000 and cut lockout rates by 25% compared to manual liquidity planning processes.</t>
+          <t>Reduced lockout rates by 25% compared to manual processes, improving customer access by addressing correspondent agent underfunding.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -632,32 +632,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BI &amp; Analytics</t>
+          <t>Analytics &amp; B.I.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Databricks dashboards for real-time data visualization and business analytics insights.</t>
+          <t>LookML for semantic modeling and KPI definition in BI tools and dashboards.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Looker dashboards to create interactive KPI tracking and performance monitoring.</t>
+          <t>Databricks dashboards for interactive business analytics and performance monitoring.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Defining and analyzing KPIs using Looker and Databricks for data-driven decision-making.</t>
+          <t>Looker dashboards for dynamic data visualization and stakeholder communication.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Building business analytics reports integrating Databricks and Looker platforms.</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Translating complex data into actionable insights with Databricks and Looker dashboards.</t>
+          <t>Quarto and R Markdown for reproducible reporting and advanced document generation.</t>
         </is>
       </c>
       <c r="L7" t="b">
@@ -672,32 +667,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Cloud &amp; MLops</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Google Cloud Platform with Vertex AI for managed machine learning workflows and BigQuery for analytics</t>
+          <t>Google Cloud Platform (Vertex AI, BigQuery, GCS) for scalable ML model development and deployment.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>AWS services including S3 for storage, Athena for SQL querying, and Glue for ETL pipelines</t>
+          <t>AWS services including S3, Athena, ECS, and Glue for data storage, query, and orchestration.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Databricks platform for collaborative data engineering and scalable machine learning model development</t>
+          <t>Kubeflow pipelines combined with CI/CD via GitHub Actions for automated ML workflows.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>AWS ECS and ECR for containerized ML model deployment and orchestration</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>EventBridge for event-driven integration supporting automated ML pipeline triggers</t>
+          <t>Model monitoring, tracking, and end-to-end ML system ownership with Terraform and ECS Fargate.</t>
         </is>
       </c>
       <c r="L8" t="b">
@@ -712,32 +702,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Data Infrastructure</t>
+          <t>Machine Learning</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Athena and S3 data lake for scalable data storage and query execution.</t>
+          <t>Logistic regression and LightGBM for predictive modeling and classification tasks.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>UUID-based data tracking to ensure data integrity and lineage.</t>
+          <t>Time series forecasting with custom feature engineering for demand and behavior prediction.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Prediction storage systems for maintaining model outputs and metrics.</t>
+          <t>K-prototypes clustering for customer segmentation and targeted marketing analytics.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Metrics storage systems supporting performance monitoring and analysis.</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Integrated data infrastructure leveraging Athena and S3 for advanced analytics.</t>
+          <t>Model evaluation using MAPE, AUC, Average Precision, and lift metrics with temporal validation.</t>
         </is>
       </c>
       <c r="L9" t="b">
@@ -752,32 +737,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Data Processing</t>
+          <t>Programming &amp; Data Tools</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Vectorization techniques for optimized Python numerical computations and data handling</t>
+          <t>Python (production ML systems, pipelines, optimization, packaging) with scikit-learn and LightGBM for predictive modeling</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Performance optimization using memory-efficient data structures and algorithms</t>
+          <t>SQL for analytical querying, data modeling, and warehouse interaction, including awswrangler integration</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Parallel processing methods to accelerate data workflows and model training</t>
+          <t>PySpark and Databricks for scalable data processing and ML workflow orchestration</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Handling large-scale data processing with expertise in datasets of hundreds of millions of rows</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Applying advanced vectorization and parallelization for scalable machine learning pipelines</t>
+          <t>Docker containerization, Git/Github, and Bash scripting for reproducible environments and MLOps automation</t>
         </is>
       </c>
       <c r="L10" t="b">
@@ -792,32 +772,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Statistics and experimentation</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Terraform for infrastructure as code and automated provisioning in cloud environments</t>
+          <t>Bayesian inference and maximum likelihood methods for robust statistical modeling and prediction.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ECS Fargate for scalable container deployment and orchestration</t>
+          <t>Bootstrapping and resampling techniques applied for model validation and uncertainty estimation.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>EventBridge scheduling to automate event-driven workflows and task execution</t>
+          <t>Experimental design and hypothesis testing to optimize causal inference and pricing experiments.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>ECR image registry for secure container image storage and management</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Integrated Terraform with ECS Fargate and ECR for streamlined ML model deployment pipelines</t>
+          <t>Summary and rolling metrics analysis for continuous performance monitoring and insights delivery.</t>
         </is>
       </c>
       <c r="L11" t="b">

--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -447,17 +447,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Developed unsupervised client segmentation model using K-prototypes, enabling targeted coupon campaigns that increased conversion rates by 20%.</t>
+          <t>Developed a client segmentation model using K-prototypes algorithm, improving targeted marketing and increasing coupon conversion rates by 20%.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Created real-time client activity monitoring system that identified churn risk, enabling timely interventions to reduce overall client attrition.</t>
+          <t>Created and implemented a real-time client activity monitoring system to identify churn risks and reduce potential customer attrition.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Designed and implemented an activity status data pipeline, improving client maturity insights and supporting strategic engagement decisions.</t>
+          <t>Designed an activity status data pipeline compiling behavioral data to support customer engagement and inform retention strategies.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -492,17 +492,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Developed and deployed a forecasting model for promotional FMCG sales, achieving 20% MAPE and enabling 21-day advance predictions.</t>
+          <t>Developed a forecasting workflow predicting promotional sales 21 days ahead with 20% MAPE, improving FMCG sales accuracy significantly.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Designed an ETL pipeline integrating sales data, facilitating daily parallel model training for each store and improving data availability.</t>
+          <t>Led creation of an orchestrated ETL pipeline to provide clean, timely sales data to supply teams, ensuring data quality and consistency.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Collaborated with MLOps team to deploy sales prediction pipelines on Vertex AI using Kubeflow, reducing processing time from 6 hours to 40 minutes.</t>
+          <t>Collaborated with ML Operations to deploy daily parallelized sales predictions, reducing processing time from 6 hours to 40 minutes.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -537,17 +537,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Developed a machine learning forecasting system achieving 10% MAPE across countries, outperforming prior manual liquidity planning methods.</t>
+          <t>Developed production-grade forecasting system predicting daily remittance volumes with 10% MAPE accuracy across multiple countries, surpassing manual methods.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Saved around $500,000 daily by reducing underfunding in a pilot country through accurate remittance volume predictions.</t>
+          <t>Saved approximately $500,000 daily by reducing underfunding in pilot country through precise liquidity forecasting and capital allocation improvements.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Reduced lockout rates by 25% compared to manual processes, improving customer access by addressing correspondent agent underfunding.</t>
+          <t>Reduced lockout rates by 25%, decreasing customer transaction blocks caused by correspondent agents' underfunding, enhancing service reliability.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -637,22 +637,22 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>LookML for semantic modeling and KPI definition in BI tools and dashboards.</t>
+          <t>LookML for semantic modeling and creating scalable BI tool frameworks.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Databricks dashboards for interactive business analytics and performance monitoring.</t>
+          <t>Developed dynamic dashboards using Looker and Databricks platforms.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Looker dashboards for dynamic data visualization and stakeholder communication.</t>
+          <t>Defined KPIs and analyzed business metrics to support data-driven decisions.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Quarto and R Markdown for reproducible reporting and advanced document generation.</t>
+          <t>Authored reproducible reports with Quarto, R Markdown, and pagedown tools.</t>
         </is>
       </c>
       <c r="L7" t="b">
@@ -672,22 +672,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Google Cloud Platform (Vertex AI, BigQuery, GCS) for scalable ML model development and deployment.</t>
+          <t>Google Cloud Platform: Vertex AI, BigQuery, Google Cloud Storage for scalable ML pipelines.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>AWS services including S3, Athena, ECS, and Glue for data storage, query, and orchestration.</t>
+          <t>AWS services: S3, Athena, ECS Fargate, ECR, Glue, EventBridge for data orchestration and storage.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Kubeflow pipelines combined with CI/CD via GitHub Actions for automated ML workflows.</t>
+          <t>Kubeflow pipelines for orchestrating batch ML workflows with CI/CD via GitHub Actions.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Model monitoring, tracking, and end-to-end ML system ownership with Terraform and ECS Fargate.</t>
+          <t>Terraform for infrastructure as code; model monitoring, tracking, and end-to-end ML system ownership.</t>
         </is>
       </c>
       <c r="L8" t="b">
@@ -712,17 +712,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Time series forecasting with custom feature engineering for demand and behavior prediction.</t>
+          <t>Time series forecasting with custom feature engineering and temporal validation techniques.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>K-prototypes clustering for customer segmentation and targeted marketing analytics.</t>
+          <t>Clustering using k-prototypes algorithm for customer segmentation and pattern discovery.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Model evaluation using MAPE, AUC, Average Precision, and lift metrics with temporal validation.</t>
+          <t>Model evaluation with metrics including MAPE, AUC, Average Precision, and lift analysis.</t>
         </is>
       </c>
       <c r="L9" t="b">
@@ -742,22 +742,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Python (production ML systems, pipelines, optimization, packaging) with scikit-learn and LightGBM for predictive modeling</t>
+          <t>Python (scikit-learn, LightGBM, pandas, NumPy) for ML pipelines, optimization, and production systems.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SQL for analytical querying, data modeling, and warehouse interaction, including awswrangler integration</t>
+          <t>R (tidyverse, tidymodels, ggplot2) for statistical modeling, experimentation, and reporting pipelines.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>PySpark and Databricks for scalable data processing and ML workflow orchestration</t>
+          <t>SQL for analytical querying, data modeling, and integration with Databricks and awswrangler.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Docker containerization, Git/Github, and Bash scripting for reproducible environments and MLOps automation</t>
+          <t>PySpark, Docker, and Bash scripting for scalable data processing, automation, and reproducible ML environments.</t>
         </is>
       </c>
       <c r="L10" t="b">
@@ -777,22 +777,22 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bayesian inference and maximum likelihood methods for robust statistical modeling and prediction.</t>
+          <t>Bayesian inference and maximum likelihood for robust statistical modeling and parameter estimation.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Bootstrapping and resampling techniques applied for model validation and uncertainty estimation.</t>
+          <t>Bootstrapping and resampling techniques to assess model stability and improve predictive accuracy.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Experimental design and hypothesis testing to optimize causal inference and pricing experiments.</t>
+          <t>Experimental design and hypothesis testing to validate business-driven data science assumptions.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Summary and rolling metrics analysis for continuous performance monitoring and insights delivery.</t>
+          <t>Summary and rolling metrics analysis for continuous monitoring of model performance and trends.</t>
         </is>
       </c>
       <c r="L11" t="b">

--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -447,17 +447,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Developed a client segmentation model using K-prototypes algorithm, improving targeted marketing and increasing coupon conversion rates by 20%.</t>
+          <t>Developed a K-prototypes clustering model for client segmentation, enabling targeted marketing campaigns and increasing coupon conversion rates by 20%.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Created and implemented a real-time client activity monitoring system to identify churn risks and reduce potential customer attrition.</t>
+          <t>Created an activity status data pipeline to monitor client engagement stages, reducing churn through early detection and personalized intervention.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Designed an activity status data pipeline compiling behavioral data to support customer engagement and inform retention strategies.</t>
+          <t>Redefined churn metrics using statistical methods to provide a robust framework for tracking client retention and behavior patterns.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -492,17 +492,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Developed a forecasting workflow predicting promotional sales 21 days ahead with 20% MAPE, improving FMCG sales accuracy significantly.</t>
+          <t>Developed an end-to-end forecasting model predicting FMCG promotional sales 21 days ahead, achieving 20% MAPE accuracy across stores.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Led creation of an orchestrated ETL pipeline to provide clean, timely sales data to supply teams, ensuring data quality and consistency.</t>
+          <t>Led creation of orchestrated ETL pipelines enabling supply teams to access clean sales data for daily demand forecasting and decision-making.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Collaborated with ML Operations to deploy daily parallelized sales predictions, reducing processing time from 6 hours to 40 minutes.</t>
+          <t>Deployed automated parallelized prediction pipeline using Vertex AI and Kubeflow, reducing daily sales forecast runtime from six hours to 40 minutes.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -537,17 +537,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Developed production-grade forecasting system predicting daily remittance volumes with 10% MAPE accuracy across multiple countries, surpassing manual methods.</t>
+          <t>Developed a production-grade forecasting model predicting daily remittance volumes with 10% MAPE across multiple countries, surpassing manual accuracy.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Saved approximately $500,000 daily by reducing underfunding in pilot country through precise liquidity forecasting and capital allocation improvements.</t>
+          <t>Built and deployed automated data pipelines integrating AWS S3 and Athena sources to ensure reliable, consistent datasets for model training and validation.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Reduced lockout rates by 25%, decreasing customer transaction blocks caused by correspondent agents' underfunding, enhancing service reliability.</t>
+          <t>Designed and implemented tree-based ensemble models (LightGBM) with time-aware validation frameworks to prevent data leakage and ensure realistic performance.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -637,22 +637,22 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>LookML for semantic modeling and creating scalable BI tool frameworks.</t>
+          <t>LookML semantic modeling for BI tools and Looker dashboards development.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Developed dynamic dashboards using Looker and Databricks platforms.</t>
+          <t>Databricks dashboards creation for interactive data visualization.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Defined KPIs and analyzed business metrics to support data-driven decisions.</t>
+          <t>KPI definition and business analytics using LookML and Databricks tools.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Authored reproducible reports with Quarto, R Markdown, and pagedown tools.</t>
+          <t>Report generation with Quarto, R Markdown, and pagedown frameworks.</t>
         </is>
       </c>
       <c r="L7" t="b">
@@ -672,22 +672,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Google Cloud Platform: Vertex AI, BigQuery, Google Cloud Storage for scalable ML pipelines.</t>
+          <t>Google Cloud Platform Vertex AI and BigQuery for scalable model training and data analysis.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>AWS services: S3, Athena, ECS Fargate, ECR, Glue, EventBridge for data orchestration and storage.</t>
+          <t>AWS Athena with S3 data lake for efficient SQL querying and storage management.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Kubeflow pipelines for orchestrating batch ML workflows with CI/CD via GitHub Actions.</t>
+          <t>Kubeflow pipelines with CI/CD via GitHub Actions for automated ML workflows and deployment.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Terraform for infrastructure as code; model monitoring, tracking, and end-to-end ML system ownership.</t>
+          <t>Model monitoring, tracking, and end-to-end ML system ownership ensuring production-grade reliability.</t>
         </is>
       </c>
       <c r="L8" t="b">
@@ -707,22 +707,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Logistic regression and LightGBM for predictive modeling and classification tasks.</t>
+          <t>Logistic regression and LightGBM for supervised model development and evaluation.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Time series forecasting with custom feature engineering and temporal validation techniques.</t>
+          <t>Time series forecasting with custom feature engineering for accurate market predictions.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Clustering using k-prototypes algorithm for customer segmentation and pattern discovery.</t>
+          <t>Clustering using k-prototypes for customer segmentation and real estate data analysis.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Model evaluation with metrics including MAPE, AUC, Average Precision, and lift analysis.</t>
+          <t>Model evaluation applying metrics MAPE, AUC, Average Precision, and lift methods.</t>
         </is>
       </c>
       <c r="L9" t="b">
@@ -742,22 +742,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Python (scikit-learn, LightGBM, pandas, NumPy) for ML pipelines, optimization, and production systems.</t>
+          <t>Python (pandas, NumPy, scikit-learn, LightGBM) for model training, evaluation, and production pipelines.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>R (tidyverse, tidymodels, ggplot2) for statistical modeling, experimentation, and reporting pipelines.</t>
+          <t>SQL for analytical querying, data modeling, and interaction with data warehouses using awswrangler.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SQL for analytical querying, data modeling, and integration with Databricks and awswrangler.</t>
+          <t>PySpark and Databricks for scalable data processing and feature engineering in ML workflows.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>PySpark, Docker, and Bash scripting for scalable data processing, automation, and reproducible ML environments.</t>
+          <t>Docker containerization with Git-based version control for reproducible environments and CI/CD integration.</t>
         </is>
       </c>
       <c r="L10" t="b">
@@ -782,17 +782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Bootstrapping and resampling techniques to assess model stability and improve predictive accuracy.</t>
+          <t>Bootstrapping and resampling techniques to improve model validation and variance estimation.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Experimental design and hypothesis testing to validate business-driven data science assumptions.</t>
+          <t>Experimental design and hypothesis testing for rigorous A/B testing and causal inference analysis.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Summary and rolling metrics analysis for continuous monitoring of model performance and trends.</t>
+          <t>Summary and rolling metrics analysis to monitor model performance and detect data drift trends.</t>
         </is>
       </c>
       <c r="L11" t="b">

--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -447,17 +447,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Developed a K-prototypes clustering model for client segmentation, enabling targeted marketing campaigns and increasing coupon conversion rates by 20%.</t>
+          <t>Developed a K-prototypes clustering model for client segmentation, enabling targeted marketing campaigns that increased coupon conversion rates by 20%.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Created an activity status data pipeline to monitor client engagement stages, reducing churn through early detection and personalized intervention.</t>
+          <t>Created a real-time client activity monitoring pipeline, “activity status,” to identify engagement stages and reduce overall churn through timely interventions.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Redefined churn metrics using statistical methods to provide a robust framework for tracking client retention and behavior patterns.</t>
+          <t>Reformulated churn metrics with statistical rigor, improving measurement accuracy and supporting data-driven retention strategies across client segments.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -492,17 +492,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Developed an end-to-end forecasting model predicting FMCG promotional sales 21 days ahead, achieving 20% MAPE accuracy across stores.</t>
+          <t>Developed and deployed a 21-day promotional sales forecasting model using LGBM, achieving 20% MAPE for FMCG demand predictions.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Led creation of orchestrated ETL pipelines enabling supply teams to access clean sales data for daily demand forecasting and decision-making.</t>
+          <t>Created an orchestrated ETL pipeline integrating product sales data for supply teams, enabling daily parallel training for store-specific models.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Deployed automated parallelized prediction pipeline using Vertex AI and Kubeflow, reducing daily sales forecast runtime from six hours to 40 minutes.</t>
+          <t>Collaborated with MLOps to deploy pipelines with Vertex AI and Kubeflow, reducing process runtime from 6 hours to 40 minutes through code optimization.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -537,17 +537,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Developed a production-grade forecasting model predicting daily remittance volumes with 10% MAPE across multiple countries, surpassing manual accuracy.</t>
+          <t>Developed a production-grade forecasting system predicting daily remittance volumes with 10% MAPE accuracy, outperforming manual processes.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Built and deployed automated data pipelines integrating AWS S3 and Athena sources to ensure reliable, consistent datasets for model training and validation.</t>
+          <t>Engineered data pipelines using AWS S3 and Athena, ensuring consistent, reliable datasets for modeling and validation workflows.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Designed and implemented tree-based ensemble models (LightGBM) with time-aware validation frameworks to prevent data leakage and ensure realistic performance.</t>
+          <t>Designed and validated tree-based ML models with LightGBM, implementing robust time-aware validation to prevent data leakage.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -637,22 +637,22 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>LookML semantic modeling for BI tools and Looker dashboards development.</t>
+          <t>LookML for semantic modeling and building scalable BI dashboards.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Databricks dashboards creation for interactive data visualization.</t>
+          <t>Databricks dashboards for real-time data visualization and KPI monitoring.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>KPI definition and business analytics using LookML and Databricks tools.</t>
+          <t>Looker dashboards to deliver actionable business insights across teams.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Report generation with Quarto, R Markdown, and pagedown frameworks.</t>
+          <t>Quarto and R Markdown for reproducible reporting and dynamic documentation.</t>
         </is>
       </c>
       <c r="L7" t="b">
@@ -672,22 +672,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Google Cloud Platform Vertex AI and BigQuery for scalable model training and data analysis.</t>
+          <t>Google Cloud Platform: Vertex AI, BigQuery, and GCS for scalable ML workflows and data storage</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>AWS Athena with S3 data lake for efficient SQL querying and storage management.</t>
+          <t>AWS ecosystem: S3, Athena, ECS Fargate, ECR, Glue, and EventBridge for data lakes and orchestration</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Kubeflow pipelines with CI/CD via GitHub Actions for automated ML workflows and deployment.</t>
+          <t>Kubeflow pipelines for batch ML pipelines, model monitoring, tracking, and deployment automation</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Model monitoring, tracking, and end-to-end ML system ownership ensuring production-grade reliability.</t>
+          <t>CI/CD with GitHub Actions and Terraform IaC for reproducible, production-grade ML system delivery</t>
         </is>
       </c>
       <c r="L8" t="b">
@@ -707,22 +707,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Logistic regression and LightGBM for supervised model development and evaluation.</t>
+          <t>LightGBM and logistic regression for classification and regression tasks with rigorous model evaluation.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Time series forecasting with custom feature engineering for accurate market predictions.</t>
+          <t>Custom feature engineering for time series forecasting using temporal validation and backtesting techniques.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Clustering using k-prototypes for customer segmentation and real estate data analysis.</t>
+          <t>Clustering with k-prototypes for customer segmentation and data-driven grouping strategies.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Model evaluation applying metrics MAPE, AUC, Average Precision, and lift methods.</t>
+          <t>Model performance metrics including MAPE, AUC, Average Precision, and lift for robust evaluation.</t>
         </is>
       </c>
       <c r="L9" t="b">
@@ -742,22 +742,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Python (pandas, NumPy, scikit-learn, LightGBM) for model training, evaluation, and production pipelines.</t>
+          <t>Python, pandas, NumPy, scikit-learn, LightGBM for model training, evaluation, and production pipelines</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SQL for analytical querying, data modeling, and interaction with data warehouses using awswrangler.</t>
+          <t>SQL and awswrangler for analytical querying, data modeling, and interaction with cloud data warehouses</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>PySpark and Databricks for scalable data processing and feature engineering in ML workflows.</t>
+          <t>PySpark and Databricks for distributed data processing and scalable machine learning workflows</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Docker containerization with Git-based version control for reproducible environments and CI/CD integration.</t>
+          <t>Docker containerization, Git, and modular Python packaging for reproducible ML environments and CI/CD integration</t>
         </is>
       </c>
       <c r="L10" t="b">
@@ -777,22 +777,22 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bayesian inference and maximum likelihood for robust statistical modeling and parameter estimation.</t>
+          <t>Applied Bayesian inference and maximum likelihood for probabilistic model evaluation and refinement.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Bootstrapping and resampling techniques to improve model validation and variance estimation.</t>
+          <t>Utilized bootstrapping and resampling techniques in Python to estimate model performance variability.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Experimental design and hypothesis testing for rigorous A/B testing and causal inference analysis.</t>
+          <t>Designed experiments and hypothesis tests to validate ML model impacts using statistical frameworks.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Summary and rolling metrics analysis to monitor model performance and detect data drift trends.</t>
+          <t>Analyzed summary and rolling metrics for continuous monitoring of model behavior over time.</t>
         </is>
       </c>
       <c r="L11" t="b">

--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -447,17 +447,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Developed a K-prototypes clustering model for client segmentation, enabling targeted marketing campaigns that increased coupon conversion rates by 20%.</t>
+          <t>Developed an unsupervised K-prototypes clustering model to segment clients using demographic and behavioral data, enabling targeted marketing campaigns.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Created a real-time client activity monitoring pipeline, “activity status,” to identify engagement stages and reduce overall churn through timely interventions.</t>
+          <t>Created a real-time client activity monitoring pipeline to identify engagement stages, reducing churn and improving campaign response rates.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Reformulated churn metrics with statistical rigor, improving measurement accuracy and supporting data-driven retention strategies across client segments.</t>
+          <t>Redesigned churn metrics with statistically robust methods to better capture client behavior and retention patterns across the platform.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -492,17 +492,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Developed and deployed a 21-day promotional sales forecasting model using LGBM, achieving 20% MAPE for FMCG demand predictions.</t>
+          <t>Designed and deployed a 21-day sales forecasting model for FMCG promotional events, achieving 20% MAPE accuracy across stores.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Created an orchestrated ETL pipeline integrating product sales data for supply teams, enabling daily parallel training for store-specific models.</t>
+          <t>Led development of an orchestrated ETL pipeline to provide clean, real-time product sales data to supply teams using SQL and Python.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Collaborated with MLOps to deploy pipelines with Vertex AI and Kubeflow, reducing process runtime from 6 hours to 40 minutes through code optimization.</t>
+          <t>Collaborated with MLOps to deploy parallelized daily sales prediction pipelines using Vertex AI and Kubeflow, reducing runtime from 6 hours to 40 minutes.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -537,17 +537,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Developed a production-grade forecasting system predicting daily remittance volumes with 10% MAPE accuracy, outperforming manual processes.</t>
+          <t>Developed a forecasting model predicting daily remittance volumes with 10% MAPE, outperforming manual processes across multiple countries.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Engineered data pipelines using AWS S3 and Athena, ensuring consistent, reliable datasets for modeling and validation workflows.</t>
+          <t>Built robust data pipelines integrating AWS S3 and Athena, enabling consistent, reliable data for accurate real-time liquidity modeling.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Designed and validated tree-based ML models with LightGBM, implementing robust time-aware validation to prevent data leakage.</t>
+          <t>Achieved daily savings of approximately $500,000 by reducing underfunding risks, driving significant capital allocation efficiency improvements.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -637,22 +637,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>LookML for semantic modeling and building scalable BI dashboards.</t>
+          <t>Defined KPIs and developed business analytics frameworks driving actionable insights.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Databricks dashboards for real-time data visualization and KPI monitoring.</t>
+          <t>Built interactive dashboards using LookML and Looker for real-time decision support.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Looker dashboards to deliver actionable business insights across teams.</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Quarto and R Markdown for reproducible reporting and dynamic documentation.</t>
+          <t>Designed and maintained Databricks dashboards with Quarto and R Markdown for reporting.</t>
         </is>
       </c>
       <c r="L7" t="b">
@@ -672,22 +667,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Google Cloud Platform: Vertex AI, BigQuery, and GCS for scalable ML workflows and data storage</t>
+          <t>Owned end-to-end batch ML pipelines on GCP and AWS using Vertex AI, Kubeflow, BigQuery, and Athena.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>AWS ecosystem: S3, Athena, ECS Fargate, ECR, Glue, and EventBridge for data lakes and orchestration</t>
+          <t>Implemented model monitoring, versioning, and CI/CD workflows with GitHub Actions and containerized ECS/Fargate deployments.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Kubeflow pipelines for batch ML pipelines, model monitoring, tracking, and deployment automation</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>CI/CD with GitHub Actions and Terraform IaC for reproducible, production-grade ML system delivery</t>
+          <t>Orchestrated large-scale data processing and vectorization, optimizing performance across S3, Glue, EventBridge, and Terraform infrastructure.</t>
         </is>
       </c>
       <c r="L8" t="b">
@@ -707,22 +697,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>LightGBM and logistic regression for classification and regression tasks with rigorous model evaluation.</t>
+          <t>Applied logistic regression, LightGBM, and tree-based models for robust predictive modeling.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Custom feature engineering for time series forecasting using temporal validation and backtesting techniques.</t>
+          <t>Engineered custom features for time series forecasting with rigorous temporal validation and backtesting.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Clustering with k-prototypes for customer segmentation and data-driven grouping strategies.</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Model performance metrics including MAPE, AUC, Average Precision, and lift for robust evaluation.</t>
+          <t>Designed clustering solutions using k-prototypes for market segmentation, optimizing model evaluation metrics.</t>
         </is>
       </c>
       <c r="L9" t="b">
@@ -742,22 +727,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Python, pandas, NumPy, scikit-learn, LightGBM for model training, evaluation, and production pipelines</t>
+          <t>Built production ML pipelines using Python, Pandas, NumPy, Scikit-learn, and LightGBM for robust market modeling.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SQL and awswrangler for analytical querying, data modeling, and interaction with cloud data warehouses</t>
+          <t>Deployed reproducible, modular ML systems with Docker, Git versioning, and automated Bash scripting on Linux environments.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>PySpark and Databricks for distributed data processing and scalable machine learning workflows</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Docker containerization, Git, and modular Python packaging for reproducible ML environments and CI/CD integration</t>
+          <t>Managed data workflows and analytics using SQL, PySpark, Databricks, and awswrangler with UUID-based tracking and packaging.</t>
         </is>
       </c>
       <c r="L10" t="b">
@@ -777,22 +757,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Applied Bayesian inference and maximum likelihood for probabilistic model evaluation and refinement.</t>
+          <t>Designed and analyzed experiments using hypothesis testing and rigorous experimental frameworks</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Utilized bootstrapping and resampling techniques in Python to estimate model performance variability.</t>
+          <t>Applied bootstrapping and resampling methods for robust statistical validation and uncertainty estimation</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Designed experiments and hypothesis tests to validate ML model impacts using statistical frameworks.</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Analyzed summary and rolling metrics for continuous monitoring of model behavior over time.</t>
+          <t>Implemented Bayesian inference and maximum likelihood techniques for advanced probabilistic modeling</t>
         </is>
       </c>
       <c r="L11" t="b">

--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -447,17 +447,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Developed an unsupervised K-prototypes clustering model to segment clients using demographic and behavioral data, enabling targeted marketing campaigns.</t>
+          <t>Developed K-prototypes segmentation model using demographic and behavioral data to enable targeted marketing campaigns and increase client engagement.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Created a real-time client activity monitoring pipeline to identify engagement stages, reducing churn and improving campaign response rates.</t>
+          <t>Built a real-time client activity monitoring pipeline to identify churn risks and improve retention by timely client re-engagement.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Redesigned churn metrics with statistically robust methods to better capture client behavior and retention patterns across the platform.</t>
+          <t>Achieved 20% increase in coupon conversion rates by directing promotions to high-propensity client segments based on model outputs.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -492,17 +492,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Designed and deployed a 21-day sales forecasting model for FMCG promotional events, achieving 20% MAPE accuracy across stores.</t>
+          <t>Developed and deployed a daily parallelized forecasting model predicting FMCG promotional event sales with 20% MAPE, improving predictability.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Led development of an orchestrated ETL pipeline to provide clean, real-time product sales data to supply teams using SQL and Python.</t>
+          <t>Led creation of ETL pipeline and performance database to provide clean data flows and monitor model KPIs, supporting supply chain decisions.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Collaborated with MLOps to deploy parallelized daily sales prediction pipelines using Vertex AI and Kubeflow, reducing runtime from 6 hours to 40 minutes.</t>
+          <t>Coordinated with ML ops team to deploy scalable sales forecast pipeline on Vertex AI and Kubeflow, reducing process duration from 6 hours to 40 minutes.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -537,17 +537,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Developed a forecasting model predicting daily remittance volumes with 10% MAPE, outperforming manual processes across multiple countries.</t>
+          <t>Developed and deployed machine learning models predicting daily remittance volumes with 10% MAPE, outperforming manual forecasting methods.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Built robust data pipelines integrating AWS S3 and Athena, enabling consistent, reliable data for accurate real-time liquidity modeling.</t>
+          <t>Built automated AWS-based data pipelines integrating S3 and Athena, ensuring reliable, consistent datasets for robust model training and validation.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Achieved daily savings of approximately $500,000 by reducing underfunding risks, driving significant capital allocation efficiency improvements.</t>
+          <t>Achieved $500,000 daily savings in underfunding for pilot country, significantly reducing liquidity management risks in correspondent agent networks.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -637,17 +637,22 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Defined KPIs and developed business analytics frameworks driving actionable insights.</t>
+          <t>Strong command of KPI definition and business analytics for actionable insights.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Built interactive dashboards using LookML and Looker for real-time decision support.</t>
+          <t>Proficient in LookML semantic modeling and creating Looker dashboards.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Designed and maintained Databricks dashboards with Quarto and R Markdown for reporting.</t>
+          <t>Experienced with Databricks dashboards for data visualization and monitoring.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Skilled in advanced reporting using Quarto, R Markdown, and pagedown.</t>
         </is>
       </c>
       <c r="L7" t="b">
@@ -667,17 +672,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Owned end-to-end batch ML pipelines on GCP and AWS using Vertex AI, Kubeflow, BigQuery, and Athena.</t>
+          <t>Proficient in AWS (S3, Athena, ECS, ECR, Glue, EventBridge) and Google Cloud Platform (Vertex AI, BigQuery, GCS).</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Implemented model monitoring, versioning, and CI/CD workflows with GitHub Actions and containerized ECS/Fargate deployments.</t>
+          <t>Experienced with Kubeflow pipelines, CI/CD workflows using GitHub Actions, and Terraform IaC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Orchestrated large-scale data processing and vectorization, optimizing performance across S3, Glue, EventBridge, and Terraform infrastructure.</t>
+          <t>Strong command of batch ML pipelines, production-grade ML system ownership, and model monitoring.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Skilled in large-scale data processing, vectorization, parallel processing, and performance optimization.</t>
         </is>
       </c>
       <c r="L8" t="b">
@@ -697,17 +707,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Applied logistic regression, LightGBM, and tree-based models for robust predictive modeling.</t>
+          <t>Strong command of LightGBM and tree-based models for predictive analytics.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Engineered custom features for time series forecasting with rigorous temporal validation and backtesting.</t>
+          <t>Proficient in time series forecasting with custom feature engineering techniques.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Designed clustering solutions using k-prototypes for market segmentation, optimizing model evaluation metrics.</t>
+          <t>Experienced with clustering using k-prototypes for effective segmentation solutions.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Skilled in model evaluation metrics including MAPE, AUC, Average Precision, and lift.</t>
         </is>
       </c>
       <c r="L9" t="b">
@@ -727,17 +742,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Built production ML pipelines using Python, Pandas, NumPy, Scikit-learn, and LightGBM for robust market modeling.</t>
+          <t>Proficient in Python, R, SQL, pandas, polars, tidyverse, and tidymodels for data science and modeling.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Deployed reproducible, modular ML systems with Docker, Git versioning, and automated Bash scripting on Linux environments.</t>
+          <t>Strong command of scikit-learn, LightGBM, kproto clustering, matplotlib, seaborn, and ggplot2 for ML and visualization.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Managed data workflows and analytics using SQL, PySpark, Databricks, and awswrangler with UUID-based tracking and packaging.</t>
+          <t>Experienced with PySpark, Databricks, awswrangler, Docker, and Linux for scalable data pipelines and deployment.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Skilled in Git, modular Python packaging, OOP, Bash scripting, and reproducible environments for ML operations.</t>
         </is>
       </c>
       <c r="L10" t="b">
@@ -757,17 +777,22 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Designed and analyzed experiments using hypothesis testing and rigorous experimental frameworks</t>
+          <t>Strong command of bootstrapping and resampling techniques for robust statistical analysis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Applied bootstrapping and resampling methods for robust statistical validation and uncertainty estimation</t>
+          <t>Proficient in experimental design and hypothesis testing for causal inference</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Implemented Bayesian inference and maximum likelihood techniques for advanced probabilistic modeling</t>
+          <t>Experienced with summary and rolling metrics analysis for performance monitoring</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Skilled in Bayesian inference and maximum likelihood estimation methods</t>
         </is>
       </c>
       <c r="L11" t="b">

--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -427,37 +427,37 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Melhor Envio</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Developed K-prototypes segmentation model using demographic and behavioral data to enable targeted marketing campaigns and increase client engagement.</t>
+          <t>Developed and deployed a 21-day FMCG promotional sales forecasting model with 20% MAPE accuracy, enabling precise inventory planning.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Built a real-time client activity monitoring pipeline to identify churn risks and improve retention by timely client re-engagement.</t>
+          <t>Designed and implemented a parallelized ETL and prediction pipeline reducing processing time from 6 hours to 40 minutes per store daily.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Achieved 20% increase in coupon conversion rates by directing promotions to high-propensity client segments based on model outputs.</t>
+          <t>Collaborated with supply and MLOps teams to integrate forecasts into ERP, preventing overstock and achieving $4 million monthly savings.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -477,32 +477,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Ria Money Transfer</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Developed and deployed a daily parallelized forecasting model predicting FMCG promotional event sales with 20% MAPE, improving predictability.</t>
+          <t>Developed a robust forecasting system predicting daily remittance volumes with 10% MAPE, improving accuracy over manual processes.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Led creation of ETL pipeline and performance database to provide clean data flows and monitor model KPIs, supporting supply chain decisions.</t>
+          <t>Engineered data pipelines integrating AWS S3 and Athena sources to ensure consistent, high-quality datasets for modeling and analysis.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Coordinated with ML ops team to deploy scalable sales forecast pipeline on Vertex AI and Kubeflow, reducing process duration from 6 hours to 40 minutes.</t>
+          <t>Designed time-aware validation frameworks to prevent data leakage, improving model reliability and producing realistic performance metrics.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -517,37 +517,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>CNCFlora</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ria Money Transfer</t>
+          <t>Data &amp; Conservation Scientist</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Developed and deployed machine learning models predicting daily remittance volumes with 10% MAPE, outperforming manual forecasting methods.</t>
+          <t>Led data integration and reproducible workflows consolidating biodiversity information to support extinction risk assessment and conservation planning in Brazil.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Built automated AWS-based data pipelines integrating S3 and Athena, ensuring reliable, consistent datasets for robust model training and validation.</t>
+          <t>Coordinated cross-disciplinary project teams executing parallel conservation initiatives targeting threatened Brazilian flora across multiple ecosystems.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Achieved $500,000 daily savings in underfunding for pilot country, significantly reducing liquidity management risks in correspondent agent networks.</t>
+          <t>Contributed extinction risk assessments for over 1,000 Brazilian plant species, aligning evaluations with IUCN Red List standards and protocols.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -637,22 +637,22 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Strong command of KPI definition and business analytics for actionable insights.</t>
+          <t>Strong command of KPI definition and business analytics for program monitoring and evaluation.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Proficient in LookML semantic modeling and creating Looker dashboards.</t>
+          <t>Proficient in creating LookML models and managing Looker dashboards for data visualization.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Experienced with Databricks dashboards for data visualization and monitoring.</t>
+          <t>Experienced with Databricks dashboards for collaborative analytics and reporting.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Skilled in advanced reporting using Quarto, R Markdown, and pagedown.</t>
+          <t>Skilled in Quarto, R Markdown, and pagedown for reproducible reporting and documentation.</t>
         </is>
       </c>
       <c r="L7" t="b">
@@ -672,22 +672,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Proficient in AWS (S3, Athena, ECS, ECR, Glue, EventBridge) and Google Cloud Platform (Vertex AI, BigQuery, GCS).</t>
+          <t>Strong command of AWS services including S3, Athena, ECS Fargate, ECR, Glue, and EventBridge scheduling.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Experienced with Kubeflow pipelines, CI/CD workflows using GitHub Actions, and Terraform IaC.</t>
+          <t>Experienced with Google Cloud Platform tools: Vertex AI, BigQuery, and GCS for data and ML workflows.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Strong command of batch ML pipelines, production-grade ML system ownership, and model monitoring.</t>
+          <t>Proficient in Kubeflow pipelines and CI/CD automation using GitHub Actions for end-to-end ML systems.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Skilled in large-scale data processing, vectorization, parallel processing, and performance optimization.</t>
+          <t>Skilled in Terraform for infrastructure as code and performance optimization in large-scale batch ML pipelines.</t>
         </is>
       </c>
       <c r="L8" t="b">
@@ -707,22 +707,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Strong command of LightGBM and tree-based models for predictive analytics.</t>
+          <t>Strong command of logistic regression, LightGBM, and tree-based models for predictive analysis.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Proficient in time series forecasting with custom feature engineering techniques.</t>
+          <t>Experienced with time series forecasting using custom feature engineering techniques.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Experienced with clustering using k-prototypes for effective segmentation solutions.</t>
+          <t>Proficient in clustering methods, specifically k-prototypes for data segmentation.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Skilled in model evaluation metrics including MAPE, AUC, Average Precision, and lift.</t>
+          <t>Skilled in model evaluation metrics including MAPE, AUC, Average Precision, and lift with temporal validation.</t>
         </is>
       </c>
       <c r="L9" t="b">
@@ -742,60 +742,25 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Proficient in Python, R, SQL, pandas, polars, tidyverse, and tidymodels for data science and modeling.</t>
+          <t>Strong command of Python, R, and SQL for statistical modeling, data querying, and production ML pipelines.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Strong command of scikit-learn, LightGBM, kproto clustering, matplotlib, seaborn, and ggplot2 for ML and visualization.</t>
+          <t>Experienced with pandas, polars, tidyverse, scikit-learn, LightGBM, and tidymodels for advanced data analysis.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Experienced with PySpark, Databricks, awswrangler, Docker, and Linux for scalable data pipelines and deployment.</t>
+          <t>Proficient in Docker containerization, Bash scripting, Linux environments, and Git for reproducible workflows.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Skilled in Git, modular Python packaging, OOP, Bash scripting, and reproducible environments for ML operations.</t>
+          <t>Hands-on with PySpark, Databricks, awswrangler, and modular Python packaging for scalable data processing.</t>
         </is>
       </c>
       <c r="L10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>skills_stack</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Statistics and experimentation</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Strong command of bootstrapping and resampling techniques for robust statistical analysis</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Proficient in experimental design and hypothesis testing for causal inference</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Experienced with summary and rolling metrics analysis for performance monitoring</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Skilled in Bayesian inference and maximum likelihood estimation methods</t>
-        </is>
-      </c>
-      <c r="L11" t="b">
         <v>1</v>
       </c>
     </row>

--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -427,37 +427,37 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Melhor Envio</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Developed and deployed a 21-day FMCG promotional sales forecasting model with 20% MAPE accuracy, enabling precise inventory planning.</t>
+          <t>Developed an unsupervised K-prototypes clustering model for client segmentation, enabling targeted marketing campaigns that increased coupon conversion by 20%.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Designed and implemented a parallelized ETL and prediction pipeline reducing processing time from 6 hours to 40 minutes per store daily.</t>
+          <t>Created and deployed a real-time client activity monitoring pipeline ("activity status") to identify churn risks and improve client retention strategies.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Collaborated with supply and MLOps teams to integrate forecasts into ERP, preventing overstock and achieving $4 million monthly savings.</t>
+          <t>Redefined churn metrics using statistical rigor, improving the accuracy of customer lifecycle insights presented to executive leadership.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -477,32 +477,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ria Money Transfer</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Developed a robust forecasting system predicting daily remittance volumes with 10% MAPE, improving accuracy over manual processes.</t>
+          <t>Delivered a forecasting system predicting FMCG promotional sales 21 days ahead, reducing overstock and saving $4 million monthly.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Engineered data pipelines integrating AWS S3 and Athena sources to ensure consistent, high-quality datasets for modeling and analysis.</t>
+          <t>Developed a parallelized, daily retrained ML pipeline using Vertex AI and Kubeflow, cutting forecast processing time from 6 hours to 40 minutes.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Designed time-aware validation frameworks to prevent data leakage, improving model reliability and producing realistic performance metrics.</t>
+          <t>Designed an experimental framework with hypothesis testing to evaluate model impact on sales and stock, ensuring statistical robustness.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -517,37 +517,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CNCFlora</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Data &amp; Conservation Scientist</t>
+          <t>Ria Money Transfer</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Led data integration and reproducible workflows consolidating biodiversity information to support extinction risk assessment and conservation planning in Brazil.</t>
+          <t>Developed a production-grade forecasting system predicting daily remittance volumes with 10% MAPE, surpassing manual accuracy reliably.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Coordinated cross-disciplinary project teams executing parallel conservation initiatives targeting threatened Brazilian flora across multiple ecosystems.</t>
+          <t>Delivered $500,000 daily savings in overfunding for pilot country by replacing manual liquidity planning with machine learning forecasts.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Contributed extinction risk assessments for over 1,000 Brazilian plant species, aligning evaluations with IUCN Red List standards and protocols.</t>
+          <t>Reduced lockout rates by 25%, minimizing customer disruptions from correspondent agent underfunding through improved predictive models.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -637,22 +637,27 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Strong command of KPI definition and business analytics for program monitoring and evaluation.</t>
+          <t>Defined KPIs and led business analytics to drive data-informed decision making.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Proficient in creating LookML models and managing Looker dashboards for data visualization.</t>
+          <t>Developed LookML semantic models to support scalable and maintainable BI solutions.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Experienced with Databricks dashboards for collaborative analytics and reporting.</t>
+          <t>Built and maintained interactive dashboards with Looker and Databricks for real-time insights.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Skilled in Quarto, R Markdown, and pagedown for reproducible reporting and documentation.</t>
+          <t>Authored reproducible analytical reports using Quarto, R Markdown, and pagedown frameworks.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Collaborated cross-functionally to align analytics outputs with strategic business objectives.</t>
         </is>
       </c>
       <c r="L7" t="b">
@@ -672,22 +677,27 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Strong command of AWS services including S3, Athena, ECS Fargate, ECR, Glue, and EventBridge scheduling.</t>
+          <t>Owned end-to-end ML systems leveraging Vertex AI, Kubeflow pipelines, BigQuery, and GCS on GCP</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Experienced with Google Cloud Platform tools: Vertex AI, BigQuery, and GCS for data and ML workflows.</t>
+          <t>Built batch ML pipelines with optimized vectorization, parallel processing, and memory efficiency for large-scale data</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Proficient in Kubeflow pipelines and CI/CD automation using GitHub Actions for end-to-end ML systems.</t>
+          <t>Implemented model monitoring, tracking, and prediction storage using AWS services including S3, Athena, ECS, and ECR</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Skilled in Terraform for infrastructure as code and performance optimization in large-scale batch ML pipelines.</t>
+          <t>Automated CI/CD workflows with GitHub Actions and managed infrastructure as code using Terraform across cloud platforms</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Scheduled event-driven workflows via AWS EventBridge and deployed containerized ML models on ECS Fargate</t>
         </is>
       </c>
       <c r="L8" t="b">
@@ -707,22 +717,27 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Strong command of logistic regression, LightGBM, and tree-based models for predictive analysis.</t>
+          <t>Built production-grade logistic regression and LightGBM models for predictive analytics and classification</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Experienced with time series forecasting using custom feature engineering techniques.</t>
+          <t>Developed time series forecasting pipelines with custom feature engineering and temporal validation</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Proficient in clustering methods, specifically k-prototypes for data segmentation.</t>
+          <t>Applied k-prototypes clustering for customer segmentation and behavioral analysis in production</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Skilled in model evaluation metrics including MAPE, AUC, Average Precision, and lift with temporal validation.</t>
+          <t>Conducted model evaluation using MAPE, AUC, average precision, and lift metrics to refine performance</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Implemented backtesting frameworks to ensure robust model generalization and deployment readiness</t>
         </is>
       </c>
       <c r="L9" t="b">
@@ -742,22 +757,27 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Strong command of Python, R, and SQL for statistical modeling, data querying, and production ML pipelines.</t>
+          <t>Developed production ML pipelines using Python, LightGBM, scikit-learn, and modular OOP architecture</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Experienced with pandas, polars, tidyverse, scikit-learn, LightGBM, and tidymodels for advanced data analysis.</t>
+          <t>Built scalable data workflows with PySpark, AWS Wrangler, Databricks, and reproducible Docker environments</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Proficient in Docker containerization, Bash scripting, Linux environments, and Git for reproducible workflows.</t>
+          <t>Designed and deployed statistical models and clustering (kproto) with R, tidymodels, and ggplot2 for experimentation</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Hands-on with PySpark, Databricks, awswrangler, and modular Python packaging for scalable data processing.</t>
+          <t>Automated data tracking and reporting pipelines using UUIDs, bash scripting, and Python packaging standards</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Implemented version control and CI workflows with Git, GitHub, and Bitbucket across analytics and ML projects</t>
         </is>
       </c>
       <c r="L10" t="b">

--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -447,17 +447,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Developed an unsupervised K-prototypes clustering model for client segmentation, enabling targeted marketing campaigns that increased coupon conversion by 20%.</t>
+          <t>Developed a client segmentation model using K-prototypes to increase targeted coupon conversion by 20%, improving marketing efficiency and engagement.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Created and deployed a real-time client activity monitoring pipeline ("activity status") to identify churn risks and improve client retention strategies.</t>
+          <t>Designed and implemented a real-time client activity monitoring pipeline enabling early churn detection and proactive retention interventions across key accounts.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Redefined churn metrics using statistical rigor, improving the accuracy of customer lifecycle insights presented to executive leadership.</t>
+          <t>Created statistically robust churn metrics reformulating definitions to align with client behavior, enhancing decision-making accuracy for retention strategies.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -492,17 +492,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Delivered a forecasting system predicting FMCG promotional sales 21 days ahead, reducing overstock and saving $4 million monthly.</t>
+          <t>Developed a forecasting model for promotional FMCG sales achieving 20% MAPE, improving event sales predictability and planning accuracy.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Developed a parallelized, daily retrained ML pipeline using Vertex AI and Kubeflow, cutting forecast processing time from 6 hours to 40 minutes.</t>
+          <t>Delivered $4 million monthly savings by preventing overstock while maintaining sales through advanced demand forecasting.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Designed an experimental framework with hypothesis testing to evaluate model impact on sales and stock, ensuring statistical robustness.</t>
+          <t>Designed and deployed an orchestrated ETL pipeline to provide clean, daily-updated sales data access for supply chain teams.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -537,17 +537,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Developed a production-grade forecasting system predicting daily remittance volumes with 10% MAPE, surpassing manual accuracy reliably.</t>
+          <t>Developed production forecasting system reducing remittance prediction time from 3 hours to 7 minutes, enabling rapid liquidity planning.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Delivered $500,000 daily savings in overfunding for pilot country by replacing manual liquidity planning with machine learning forecasts.</t>
+          <t>Achieved 10% MAPE forecasting accuracy across multiple countries, improving predictability compared to manual methods and increasing forecast reliability.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Reduced lockout rates by 25%, minimizing customer disruptions from correspondent agent underfunding through improved predictive models.</t>
+          <t>Generated $200,000 daily savings by minimizing overfunding in pilot market, driving significant capital efficiency in international remittance operations.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -637,27 +637,22 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Defined KPIs and led business analytics to drive data-informed decision making.</t>
+          <t>Defined KPIs and developed business analytics frameworks for actionable decision support</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Developed LookML semantic models to support scalable and maintainable BI solutions.</t>
+          <t>Built and maintained Looker and Databricks dashboards for cross-team data visualization</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Built and maintained interactive dashboards with Looker and Databricks for real-time insights.</t>
+          <t>Authored reproducible reports using Quarto, R Markdown, and pagedown to communicate insights</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Authored reproducible analytical reports using Quarto, R Markdown, and pagedown frameworks.</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Collaborated cross-functionally to align analytics outputs with strategic business objectives.</t>
+          <t>Implemented semantic modeling with LookML to streamline BI data access and consistency</t>
         </is>
       </c>
       <c r="L7" t="b">
@@ -677,27 +672,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Owned end-to-end ML systems leveraging Vertex AI, Kubeflow pipelines, BigQuery, and GCS on GCP</t>
+          <t>Production-grade ML pipelines with Vertex AI, Kubeflow, GitHub Actions, and Terraform infrastructure as code</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Built batch ML pipelines with optimized vectorization, parallel processing, and memory efficiency for large-scale data</t>
+          <t>Built large-scale data workflows processing hundreds of millions of rows using BigQuery, Athena, and S3 data lakes</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Implemented model monitoring, tracking, and prediction storage using AWS services including S3, Athena, ECS, and ECR</t>
+          <t>Monitored and tracked models with prediction storage, performance optimization, and parallel processing techniques</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Automated CI/CD workflows with GitHub Actions and managed infrastructure as code using Terraform across cloud platforms</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Scheduled event-driven workflows via AWS EventBridge and deployed containerized ML models on ECS Fargate</t>
+          <t>Led end-to-end ML deployment on AWS ECS Fargate with ECR images and EventBridge scheduling integration</t>
         </is>
       </c>
       <c r="L8" t="b">
@@ -717,27 +707,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Built production-grade logistic regression and LightGBM models for predictive analytics and classification</t>
+          <t>Developed time series forecasting models with custom feature engineering and robust temporal validation</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Developed time series forecasting pipelines with custom feature engineering and temporal validation</t>
+          <t>Applied logistic regression and LightGBM for classification and predictive modeling with rigorous evaluation metrics</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Applied k-prototypes clustering for customer segmentation and behavioral analysis in production</t>
+          <t>Implemented clustering using k-prototypes for customer segmentation to enhance behavioral analytics</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Conducted model evaluation using MAPE, AUC, average precision, and lift metrics to refine performance</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Implemented backtesting frameworks to ensure robust model generalization and deployment readiness</t>
+          <t>Evaluated model performance with MAPE, AUC, average precision, and lift for reliable business impact assessment</t>
         </is>
       </c>
       <c r="L9" t="b">
@@ -757,27 +742,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Developed production ML pipelines using Python, LightGBM, scikit-learn, and modular OOP architecture</t>
+          <t>Built production ML pipelines in Python using modular architecture, packaging, and Docker containerization</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Built scalable data workflows with PySpark, AWS Wrangler, Databricks, and reproducible Docker environments</t>
+          <t>Applied advanced statistical modeling and experimentation frameworks in R with tidyverse and tidymodels</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Designed and deployed statistical models and clustering (kproto) with R, tidymodels, and ggplot2 for experimentation</t>
+          <t>Optimized large-scale data workflows using SQL, PySpark, Databricks, and awswrangler in cloud environments</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Automated data tracking and reporting pipelines using UUIDs, bash scripting, and Python packaging standards</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Implemented version control and CI workflows with Git, GitHub, and Bitbucket across analytics and ML projects</t>
+          <t>Collaborated on reproducible analysis and data tracking with Git, UUID systems, and Bash automation scripting</t>
         </is>
       </c>
       <c r="L10" t="b">

--- a/data/cv_render_new.xlsx
+++ b/data/cv_render_new.xlsx
@@ -427,37 +427,37 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Melhor Envio</t>
+          <t>PicPay</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Developed a client segmentation model using K-prototypes to increase targeted coupon conversion by 20%, improving marketing efficiency and engagement.</t>
+          <t>Led redesign and A/B testing of PicPay home page, reducing click-through rate time by 20%, improving user engagement metrics.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Designed and implemented a real-time client activity monitoring pipeline enabling early churn detection and proactive retention interventions across key accounts.</t>
+          <t>Designed and analyzed randomized experiments to measure product changes, ensuring statistical rigor and actionable insights for product teams.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Created statistically robust churn metrics reformulating definitions to align with client behavior, enhancing decision-making accuracy for retention strategies.</t>
+          <t>Recreated and validated client segmentation model using Gaussian Mixture Modeling, applying feature engineering and hypothesis testing.</t>
         </is>
       </c>
       <c r="L2" t="b">
@@ -492,17 +492,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Developed a forecasting model for promotional FMCG sales achieving 20% MAPE, improving event sales predictability and planning accuracy.</t>
+          <t>Developed and deployed a forecasting model predicting FMCG promotional sales 21 days ahead, improving event sales predictability to 20% MAPE.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Delivered $4 million monthly savings by preventing overstock while maintaining sales through advanced demand forecasting.</t>
+          <t>Led creation of an ETL pipeline and performance database to monitor forecasting model KPIs and facilitate cross-team transparency.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Designed and deployed an orchestrated ETL pipeline to provide clean, daily-updated sales data access for supply chain teams.</t>
+          <t>Designed causal inference experiments to evaluate model impact on sales and inventory, enabling data-driven supply chain decisions.</t>
         </is>
       </c>
       <c r="L3" t="b">
@@ -537,17 +537,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Developed production forecasting system reducing remittance prediction time from 3 hours to 7 minutes, enabling rapid liquidity planning.</t>
+          <t>Developed a forecasting system achieving 10% MAPE accuracy for multiple countries, improving predictability over the manual process.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Achieved 10% MAPE forecasting accuracy across multiple countries, improving predictability compared to manual methods and increasing forecast reliability.</t>
+          <t>Saved approximately $200,000 daily by reducing overfunding in a pilot country through optimized remittance volume predictions.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Generated $200,000 daily savings by minimizing overfunding in pilot market, driving significant capital efficiency in international remittance operations.</t>
+          <t>Decreased lockout rates by 25% versus manual methods, enhancing customer access and reducing underfunding of correspondent agents.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -632,27 +632,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Analytics &amp; B.I.</t>
+          <t>Statistics and experimentation</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Defined KPIs and developed business analytics frameworks for actionable decision support</t>
+          <t>Applied experimental design and A/B testing for causal inference and hypothesis validation.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Built and maintained Looker and Databricks dashboards for cross-team data visualization</t>
+          <t>Leveraged bootstrapping and resampling techniques to enhance statistical robustness in analyses.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Authored reproducible reports using Quarto, R Markdown, and pagedown to communicate insights</t>
+          <t>Developed Bayesian inference and maximum likelihood models to support evidence-driven decisions.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Implemented semantic modeling with LookML to streamline BI data access and consistency</t>
+          <t>Performed summary and rolling metrics analysis to track trends and inform iterative improvements.</t>
         </is>
       </c>
       <c r="L7" t="b">
@@ -667,27 +667,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cloud &amp; MLops</t>
+          <t>Programming &amp; Data Tools</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Production-grade ML pipelines with Vertex AI, Kubeflow, GitHub Actions, and Terraform infrastructure as code</t>
+          <t>Designed and deployed production ML pipelines with Python, PySpark, Docker, and modular architecture patterns</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Built large-scale data workflows processing hundreds of millions of rows using BigQuery, Athena, and S3 data lakes</t>
+          <t>Led experimentation and causal inference analyses using R, tidymodels, and kproto clustering for robust insights</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Monitored and tracked models with prediction storage, performance optimization, and parallel processing techniques</t>
+          <t>Optimized large-scale data workflows via SQL, awswrangler, Databricks, and reproducible Linux environments</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Led end-to-end ML deployment on AWS ECS Fargate with ECR images and EventBridge scheduling integration</t>
+          <t>Collaborated cross-functionally to integrate Git-based versioning, Python packaging, and automated Bash scripting in analytics</t>
         </is>
       </c>
       <c r="L8" t="b">
@@ -707,22 +707,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Developed time series forecasting models with custom feature engineering and robust temporal validation</t>
+          <t>Strong command of time series forecasting with custom feature engineering and temporal validation techniques</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Applied logistic regression and LightGBM for classification and predictive modeling with rigorous evaluation metrics</t>
+          <t>Developed and validated tree-based models using LightGBM and logistic regression for high-impact applications</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Implemented clustering using k-prototypes for customer segmentation to enhance behavioral analytics</t>
+          <t>Performed rigorous model evaluation using MAPE, AUC, average precision, and lift metrics to ensure accuracy</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Evaluated model performance with MAPE, AUC, average precision, and lift for reliable business impact assessment</t>
+          <t>Applied k-prototypes clustering for effective customer segmentation supporting targeted analytical insights</t>
         </is>
       </c>
       <c r="L9" t="b">
@@ -737,27 +737,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Programming &amp; Data Tools</t>
+          <t>Analytics &amp; B.I.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Built production ML pipelines in Python using modular architecture, packaging, and Docker containerization</t>
+          <t>Defined KPIs and delivered actionable business analytics driving strategic decisions</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Applied advanced statistical modeling and experimentation frameworks in R with tidyverse and tidymodels</t>
+          <t>Developed and maintained LookML semantic models for scalable BI dashboard solutions</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Optimized large-scale data workflows using SQL, PySpark, Databricks, and awswrangler in cloud environments</t>
+          <t>Built interactive Looker and Databricks dashboards to visualize key operational metrics</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Collaborated on reproducible analysis and data tracking with Git, UUID systems, and Bash automation scripting</t>
+          <t>Authored reproducible reports with Quarto, R Markdown, and pagedown for stakeholder communication</t>
         </is>
       </c>
       <c r="L10" t="b">
